--- a/src/outputs/ta_schedule-final.xlsx
+++ b/src/outputs/ta_schedule-final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB0BE0C-DAE6-4DDD-B2E4-3F09596A6AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9000F71-74F2-4BE1-8E62-C330786C23A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,6 +36,30 @@
     <t>Session, 1 (8:15AM - 9:15 AM)</t>
   </si>
   <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>Debora Sarpomaa Boateng</t>
+  </si>
+  <si>
+    <t>RMA</t>
+  </si>
+  <si>
+    <t>Evans Tignanlene Nkumicha</t>
+  </si>
+  <si>
+    <t>RMB</t>
+  </si>
+  <si>
+    <t>Isaac Ayensu</t>
+  </si>
+  <si>
+    <t>VSLA</t>
+  </si>
+  <si>
+    <t>Lucian Nsiah Sarkodie / Ebenezer Paa Effisah</t>
+  </si>
+  <si>
     <t>206</t>
   </si>
   <si>
@@ -54,30 +78,6 @@
     <t>David Nkansah Mensah</t>
   </si>
   <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>Debora Sarpomaa Boateng</t>
-  </si>
-  <si>
-    <t>RMA</t>
-  </si>
-  <si>
-    <t>Evans Tignanlene Nkumicha</t>
-  </si>
-  <si>
-    <t>RMB</t>
-  </si>
-  <si>
-    <t>Isaac Ayensu</t>
-  </si>
-  <si>
-    <t>VSLA</t>
-  </si>
-  <si>
-    <t>Lucian Nsiah Sarkodie / Ebenezer Paa Effisah</t>
-  </si>
-  <si>
     <t>N1</t>
   </si>
   <si>
@@ -195,6 +195,18 @@
     <t>Session, 2  (10:00AM - 11:00 AM)</t>
   </si>
   <si>
+    <t>Mansur Abubakar</t>
+  </si>
+  <si>
+    <t>Prince Asare Ange Seraphin</t>
+  </si>
+  <si>
+    <t>Archer Michaelina Adu</t>
+  </si>
+  <si>
+    <t>Prince Nyame / Effa Emmanuel</t>
+  </si>
+  <si>
     <t>Ashanti Atta Al-Hafid</t>
   </si>
   <si>
@@ -204,18 +216,6 @@
     <t>Lilian Amankwa</t>
   </si>
   <si>
-    <t>Mansur Abubakar</t>
-  </si>
-  <si>
-    <t>Prince Asare Ange Seraphin</t>
-  </si>
-  <si>
-    <t>Archer Michaelina Adu</t>
-  </si>
-  <si>
-    <t>Prince Nyame / Effa Emmanuel</t>
-  </si>
-  <si>
     <t>Alex Ohemeng Adusei</t>
   </si>
   <si>
@@ -282,6 +282,12 @@
     <t>Session, 3 (11:45AM - 12:45 PM)</t>
   </si>
   <si>
+    <t>Erica Gado</t>
+  </si>
+  <si>
+    <t>Richmond Donkor / Lawrence Cudjoe</t>
+  </si>
+  <si>
     <t>Dickson Avonor</t>
   </si>
   <si>
@@ -291,12 +297,6 @@
     <t>Papa Tawiah</t>
   </si>
   <si>
-    <t>Erica Gado</t>
-  </si>
-  <si>
-    <t>Richmond Donkor / Lawrence Cudjoe</t>
-  </si>
-  <si>
     <t>Bernard Eshun</t>
   </si>
   <si>
@@ -369,6 +369,12 @@
     <t>Session, 5 (3:15PM - 4:15 PM)</t>
   </si>
   <si>
+    <t>Poku Antwi Kwadwo</t>
+  </si>
+  <si>
+    <t>Lilian Amankwa / Mansur Abubakar</t>
+  </si>
+  <si>
     <t>Samuel Agbenu</t>
   </si>
   <si>
@@ -378,12 +384,6 @@
     <t>Kwasi Kyei Sarpong</t>
   </si>
   <si>
-    <t>Poku Antwi Kwadwo</t>
-  </si>
-  <si>
-    <t>Lilian Amankwa / Mansur Abubakar</t>
-  </si>
-  <si>
     <t>Prince Nyame</t>
   </si>
   <si>
@@ -399,21 +399,21 @@
     <t>Session, 6 (5:00PM - 6:00 PM)</t>
   </si>
   <si>
+    <t>Edmond Khan</t>
+  </si>
+  <si>
+    <t>Darkwah Kingsley Awuah</t>
+  </si>
+  <si>
+    <t>Doreen Asamoah / Papa Tawiah</t>
+  </si>
+  <si>
     <t>Lucas Biiyiin</t>
   </si>
   <si>
     <t>Gideon Kuffour Agyekum</t>
   </si>
   <si>
-    <t>Edmond Khan</t>
-  </si>
-  <si>
-    <t>Darkwah Kingsley Awuah</t>
-  </si>
-  <si>
-    <t>Doreen Asamoah / Papa Tawiah</t>
-  </si>
-  <si>
     <t>Richmond Donkor</t>
   </si>
   <si>
@@ -432,13 +432,13 @@
     <t>Session, 1 (8:15 AM - 9:15 AM)</t>
   </si>
   <si>
+    <t>Wafawu Mashud</t>
+  </si>
+  <si>
+    <t>David Nkansah Mensah / Debora Sarpomaa Boateng</t>
+  </si>
+  <si>
     <t>Barnabas Banahene-Owusu</t>
-  </si>
-  <si>
-    <t>Wafawu Mashud</t>
-  </si>
-  <si>
-    <t>David Nkansah Mensah / Debora Sarpomaa Boateng</t>
   </si>
   <si>
     <t>Session, 2 (10:00 AM - 11:00 AM)</t>
@@ -1019,7 +1019,7 @@
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1800,7 +1800,7 @@
         <v>87</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
         <v>89</v>
@@ -1814,7 +1814,7 @@
         <v>87</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
         <v>90</v>
@@ -1828,7 +1828,7 @@
         <v>87</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
         <v>91</v>
@@ -2094,10 +2094,10 @@
         <v>110</v>
       </c>
       <c r="C80" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -2108,10 +2108,10 @@
         <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -2122,10 +2122,10 @@
         <v>110</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D82" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -2136,10 +2136,10 @@
         <v>110</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -2153,7 +2153,7 @@
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -2419,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="D104" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
@@ -2447,7 +2447,7 @@
         <v>12</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
@@ -2461,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -2475,7 +2475,7 @@
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -2503,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
@@ -2517,7 +2517,7 @@
         <v>22</v>
       </c>
       <c r="D111" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -2769,7 +2769,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
@@ -2783,7 +2783,7 @@
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
@@ -2797,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="D132" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
@@ -2825,7 +2825,7 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
@@ -2839,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
@@ -2867,7 +2867,7 @@
         <v>24</v>
       </c>
       <c r="D137" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
@@ -3077,7 +3077,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
@@ -3091,7 +3091,7 @@
         <v>8</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
@@ -3105,7 +3105,7 @@
         <v>10</v>
       </c>
       <c r="D155" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
@@ -3133,7 +3133,7 @@
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
@@ -3147,7 +3147,7 @@
         <v>16</v>
       </c>
       <c r="D158" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
@@ -3175,7 +3175,7 @@
         <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
@@ -3189,7 +3189,7 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
@@ -3438,10 +3438,10 @@
         <v>141</v>
       </c>
       <c r="C180" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
@@ -3452,10 +3452,10 @@
         <v>141</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D181" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
@@ -3466,10 +3466,10 @@
         <v>141</v>
       </c>
       <c r="C182" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
@@ -3480,10 +3480,10 @@
         <v>141</v>
       </c>
       <c r="C183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
@@ -3497,7 +3497,7 @@
         <v>16</v>
       </c>
       <c r="D184" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
@@ -3511,7 +3511,7 @@
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
@@ -3525,7 +3525,7 @@
         <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
@@ -3539,7 +3539,7 @@
         <v>22</v>
       </c>
       <c r="D187" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
@@ -3553,7 +3553,7 @@
         <v>24</v>
       </c>
       <c r="D188" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
@@ -3805,7 +3805,7 @@
         <v>8</v>
       </c>
       <c r="D207" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
@@ -3819,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="D208" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.35">
@@ -3833,7 +3833,7 @@
         <v>12</v>
       </c>
       <c r="D209" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.35">
@@ -3847,7 +3847,7 @@
         <v>14</v>
       </c>
       <c r="D210" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.35">
@@ -3861,7 +3861,7 @@
         <v>16</v>
       </c>
       <c r="D211" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.35">
@@ -3875,7 +3875,7 @@
         <v>18</v>
       </c>
       <c r="D212" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.35">
@@ -3889,7 +3889,7 @@
         <v>20</v>
       </c>
       <c r="D213" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.35">
@@ -3903,7 +3903,7 @@
         <v>22</v>
       </c>
       <c r="D214" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.35">
@@ -4155,7 +4155,7 @@
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>139</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
@@ -4197,7 +4197,7 @@
         <v>12</v>
       </c>
       <c r="D236" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.35">
@@ -4211,7 +4211,7 @@
         <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.35">
@@ -4239,7 +4239,7 @@
         <v>18</v>
       </c>
       <c r="D239" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.35">
@@ -4519,7 +4519,7 @@
         <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
@@ -4561,7 +4561,7 @@
         <v>12</v>
       </c>
       <c r="D263" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
@@ -4575,7 +4575,7 @@
         <v>14</v>
       </c>
       <c r="D264" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.35">
@@ -4603,7 +4603,7 @@
         <v>18</v>
       </c>
       <c r="D266" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.35">
@@ -4883,7 +4883,7 @@
         <v>6</v>
       </c>
       <c r="D287" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.35">
@@ -4897,7 +4897,7 @@
         <v>8</v>
       </c>
       <c r="D288" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.35">
@@ -4939,7 +4939,7 @@
         <v>14</v>
       </c>
       <c r="D291" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.35">
@@ -4953,7 +4953,7 @@
         <v>16</v>
       </c>
       <c r="D292" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.35">
@@ -4967,7 +4967,7 @@
         <v>18</v>
       </c>
       <c r="D293" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.35">
@@ -5205,7 +5205,7 @@
         <v>52</v>
       </c>
       <c r="D310" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.35">
@@ -5247,7 +5247,7 @@
         <v>6</v>
       </c>
       <c r="D314" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.35">
@@ -5261,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="D315" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.35">
@@ -5275,7 +5275,7 @@
         <v>10</v>
       </c>
       <c r="D316" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.35">
@@ -5289,7 +5289,7 @@
         <v>12</v>
       </c>
       <c r="D317" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.35">
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="D318" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.35">
@@ -5317,7 +5317,7 @@
         <v>16</v>
       </c>
       <c r="D319" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.35">
@@ -5331,7 +5331,7 @@
         <v>18</v>
       </c>
       <c r="D320" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.35">
@@ -5555,7 +5555,7 @@
         <v>50</v>
       </c>
       <c r="D336" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.35">
@@ -5569,7 +5569,7 @@
         <v>52</v>
       </c>
       <c r="D337" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.35">
@@ -5611,7 +5611,7 @@
         <v>6</v>
       </c>
       <c r="D341" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.35">
@@ -5625,7 +5625,7 @@
         <v>8</v>
       </c>
       <c r="D342" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.35">
@@ -5639,7 +5639,7 @@
         <v>10</v>
       </c>
       <c r="D343" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.35">
@@ -5653,7 +5653,7 @@
         <v>12</v>
       </c>
       <c r="D344" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.35">
@@ -5667,7 +5667,7 @@
         <v>14</v>
       </c>
       <c r="D345" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.35">
@@ -5681,7 +5681,7 @@
         <v>16</v>
       </c>
       <c r="D346" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.35">
@@ -5695,7 +5695,7 @@
         <v>18</v>
       </c>
       <c r="D347" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.35">
@@ -5919,7 +5919,7 @@
         <v>50</v>
       </c>
       <c r="D363" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.35">
@@ -5933,7 +5933,7 @@
         <v>52</v>
       </c>
       <c r="D364" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.35">
@@ -5975,7 +5975,7 @@
         <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.35">
@@ -5989,7 +5989,7 @@
         <v>8</v>
       </c>
       <c r="D369" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.35">
@@ -6003,7 +6003,7 @@
         <v>10</v>
       </c>
       <c r="D370" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.35">
@@ -6017,7 +6017,7 @@
         <v>12</v>
       </c>
       <c r="D371" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.35">
@@ -6031,7 +6031,7 @@
         <v>14</v>
       </c>
       <c r="D372" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.35">
@@ -6045,7 +6045,7 @@
         <v>16</v>
       </c>
       <c r="D373" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.35">
@@ -6059,7 +6059,7 @@
         <v>18</v>
       </c>
       <c r="D374" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.35">
@@ -6255,7 +6255,7 @@
         <v>46</v>
       </c>
       <c r="D388" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.35">
@@ -6283,7 +6283,7 @@
         <v>50</v>
       </c>
       <c r="D390" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.35">
@@ -6297,7 +6297,7 @@
         <v>52</v>
       </c>
       <c r="D391" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.35">
@@ -6339,7 +6339,7 @@
         <v>6</v>
       </c>
       <c r="D395" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.35">
@@ -6353,7 +6353,7 @@
         <v>8</v>
       </c>
       <c r="D396" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.35">
@@ -6367,7 +6367,7 @@
         <v>10</v>
       </c>
       <c r="D397" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.35">
@@ -6381,7 +6381,7 @@
         <v>12</v>
       </c>
       <c r="D398" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.35">
@@ -6395,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="D399" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.35">
@@ -6409,7 +6409,7 @@
         <v>16</v>
       </c>
       <c r="D400" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.35">
@@ -6423,7 +6423,7 @@
         <v>18</v>
       </c>
       <c r="D401" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.35">
@@ -6591,7 +6591,7 @@
         <v>42</v>
       </c>
       <c r="D413" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.35">
@@ -6605,7 +6605,7 @@
         <v>44</v>
       </c>
       <c r="D414" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.35">
@@ -6619,7 +6619,7 @@
         <v>46</v>
       </c>
       <c r="D415" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.35">
@@ -6647,7 +6647,7 @@
         <v>50</v>
       </c>
       <c r="D417" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.35">
@@ -6661,7 +6661,7 @@
         <v>52</v>
       </c>
       <c r="D418" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.35">
@@ -6703,7 +6703,7 @@
         <v>6</v>
       </c>
       <c r="D422" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.35">
@@ -6717,7 +6717,7 @@
         <v>8</v>
       </c>
       <c r="D423" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.35">
@@ -6731,7 +6731,7 @@
         <v>10</v>
       </c>
       <c r="D424" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.35">
@@ -6745,7 +6745,7 @@
         <v>12</v>
       </c>
       <c r="D425" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.35">
@@ -6759,7 +6759,7 @@
         <v>14</v>
       </c>
       <c r="D426" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.35">
@@ -6773,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="D427" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.35">
@@ -6787,7 +6787,7 @@
         <v>18</v>
       </c>
       <c r="D428" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.35">
@@ -6969,7 +6969,7 @@
         <v>46</v>
       </c>
       <c r="D441" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.35">
@@ -6997,7 +6997,7 @@
         <v>50</v>
       </c>
       <c r="D443" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.35">
@@ -7011,7 +7011,7 @@
         <v>52</v>
       </c>
       <c r="D444" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.35">
@@ -7025,7 +7025,7 @@
         <v>54</v>
       </c>
       <c r="D445" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.35">
@@ -7053,7 +7053,7 @@
         <v>6</v>
       </c>
       <c r="D448" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.35">
@@ -7067,7 +7067,7 @@
         <v>8</v>
       </c>
       <c r="D449" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.35">
@@ -7078,10 +7078,10 @@
         <v>162</v>
       </c>
       <c r="C450" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D450" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.35">
@@ -7092,10 +7092,10 @@
         <v>162</v>
       </c>
       <c r="C451" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D451" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.35">
@@ -7106,10 +7106,10 @@
         <v>162</v>
       </c>
       <c r="C452" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D452" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.35">
@@ -7120,10 +7120,10 @@
         <v>162</v>
       </c>
       <c r="C453" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D453" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.35">
@@ -7305,7 +7305,7 @@
         <v>50</v>
       </c>
       <c r="D466" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.35">
@@ -7319,7 +7319,7 @@
         <v>52</v>
       </c>
       <c r="D467" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.35">
@@ -7333,7 +7333,7 @@
         <v>54</v>
       </c>
       <c r="D468" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.35">
@@ -7361,7 +7361,7 @@
         <v>6</v>
       </c>
       <c r="D471" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.35">
@@ -7375,7 +7375,7 @@
         <v>8</v>
       </c>
       <c r="D472" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.35">
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="D473" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.35">
@@ -7403,7 +7403,7 @@
         <v>12</v>
       </c>
       <c r="D474" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.35">
@@ -7417,7 +7417,7 @@
         <v>14</v>
       </c>
       <c r="D475" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.35">
@@ -7431,7 +7431,7 @@
         <v>16</v>
       </c>
       <c r="D476" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.35">
@@ -7445,7 +7445,7 @@
         <v>18</v>
       </c>
       <c r="D477" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.35">
@@ -7627,7 +7627,7 @@
         <v>44</v>
       </c>
       <c r="D490" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.35">
@@ -7641,7 +7641,7 @@
         <v>46</v>
       </c>
       <c r="D491" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.35">
@@ -7669,7 +7669,7 @@
         <v>50</v>
       </c>
       <c r="D493" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.35">
@@ -7683,7 +7683,7 @@
         <v>52</v>
       </c>
       <c r="D494" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.35">
@@ -7697,7 +7697,7 @@
         <v>54</v>
       </c>
       <c r="D495" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.35">
@@ -7725,7 +7725,7 @@
         <v>6</v>
       </c>
       <c r="D498" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.35">
@@ -7739,7 +7739,7 @@
         <v>8</v>
       </c>
       <c r="D499" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.35">
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="D500" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.35">
@@ -7767,7 +7767,7 @@
         <v>12</v>
       </c>
       <c r="D501" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.35">
@@ -7781,7 +7781,7 @@
         <v>14</v>
       </c>
       <c r="D502" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.35">
@@ -7795,7 +7795,7 @@
         <v>16</v>
       </c>
       <c r="D503" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.35">
@@ -7809,7 +7809,7 @@
         <v>18</v>
       </c>
       <c r="D504" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.35">
@@ -8005,7 +8005,7 @@
         <v>46</v>
       </c>
       <c r="D518" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.35">
@@ -8033,7 +8033,7 @@
         <v>50</v>
       </c>
       <c r="D520" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.35">
@@ -8047,7 +8047,7 @@
         <v>52</v>
       </c>
       <c r="D521" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.35">
@@ -8061,7 +8061,7 @@
         <v>54</v>
       </c>
       <c r="D522" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.35">
@@ -8089,7 +8089,7 @@
         <v>6</v>
       </c>
       <c r="D525" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.35">
@@ -8103,7 +8103,7 @@
         <v>8</v>
       </c>
       <c r="D526" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.35">
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="D527" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.35">
@@ -8131,7 +8131,7 @@
         <v>12</v>
       </c>
       <c r="D528" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.35">
@@ -8145,7 +8145,7 @@
         <v>14</v>
       </c>
       <c r="D529" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.35">
@@ -8159,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="D530" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.35">
@@ -8173,7 +8173,7 @@
         <v>18</v>
       </c>
       <c r="D531" t="s">
-        <v>185</v>
+        <v>94</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.35">
@@ -8327,7 +8327,7 @@
         <v>40</v>
       </c>
       <c r="D542" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.35">
@@ -8341,7 +8341,7 @@
         <v>42</v>
       </c>
       <c r="D543" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.35">
@@ -8355,7 +8355,7 @@
         <v>44</v>
       </c>
       <c r="D544" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.35">
@@ -8369,7 +8369,7 @@
         <v>46</v>
       </c>
       <c r="D545" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.35">
@@ -8383,7 +8383,7 @@
         <v>48</v>
       </c>
       <c r="D546" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.35">
@@ -8397,7 +8397,7 @@
         <v>50</v>
       </c>
       <c r="D547" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.35">
@@ -8411,7 +8411,7 @@
         <v>52</v>
       </c>
       <c r="D548" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.35">
@@ -8425,7 +8425,7 @@
         <v>54</v>
       </c>
       <c r="D549" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.35">
@@ -8453,7 +8453,7 @@
         <v>6</v>
       </c>
       <c r="D552" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.35">
@@ -8467,7 +8467,7 @@
         <v>8</v>
       </c>
       <c r="D553" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.35">
@@ -8481,7 +8481,7 @@
         <v>10</v>
       </c>
       <c r="D554" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.35">
@@ -8495,7 +8495,7 @@
         <v>12</v>
       </c>
       <c r="D555" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.35">
@@ -8509,7 +8509,7 @@
         <v>14</v>
       </c>
       <c r="D556" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.35">
@@ -8523,7 +8523,7 @@
         <v>16</v>
       </c>
       <c r="D557" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.35">
@@ -8537,7 +8537,7 @@
         <v>18</v>
       </c>
       <c r="D558" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.35">
@@ -8663,7 +8663,7 @@
         <v>36</v>
       </c>
       <c r="D567" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.35">
@@ -8677,7 +8677,7 @@
         <v>38</v>
       </c>
       <c r="D568" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.35">
@@ -8691,7 +8691,7 @@
         <v>40</v>
       </c>
       <c r="D569" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.35">
@@ -8705,7 +8705,7 @@
         <v>42</v>
       </c>
       <c r="D570" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.35">
@@ -8719,7 +8719,7 @@
         <v>44</v>
       </c>
       <c r="D571" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.35">
@@ -8733,7 +8733,7 @@
         <v>46</v>
       </c>
       <c r="D572" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.35">
@@ -8747,7 +8747,7 @@
         <v>48</v>
       </c>
       <c r="D573" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.35">
@@ -8761,7 +8761,7 @@
         <v>50</v>
       </c>
       <c r="D574" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.35">
@@ -8775,7 +8775,7 @@
         <v>52</v>
       </c>
       <c r="D575" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.35">
@@ -8789,7 +8789,7 @@
         <v>54</v>
       </c>
       <c r="D576" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.35">
@@ -8817,7 +8817,7 @@
         <v>6</v>
       </c>
       <c r="D579" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.35">
@@ -8831,7 +8831,7 @@
         <v>8</v>
       </c>
       <c r="D580" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.35">
@@ -8845,7 +8845,7 @@
         <v>10</v>
       </c>
       <c r="D581" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.35">
@@ -8859,7 +8859,7 @@
         <v>12</v>
       </c>
       <c r="D582" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.35">
@@ -8873,7 +8873,7 @@
         <v>14</v>
       </c>
       <c r="D583" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.35">
@@ -8887,7 +8887,7 @@
         <v>16</v>
       </c>
       <c r="D584" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.35">
@@ -8901,7 +8901,7 @@
         <v>18</v>
       </c>
       <c r="D585" t="s">
-        <v>189</v>
+        <v>70</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.35">
@@ -9041,7 +9041,7 @@
         <v>38</v>
       </c>
       <c r="D595" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.35">
@@ -9055,7 +9055,7 @@
         <v>40</v>
       </c>
       <c r="D596" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.35">
@@ -9069,7 +9069,7 @@
         <v>42</v>
       </c>
       <c r="D597" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.35">
@@ -9083,7 +9083,7 @@
         <v>44</v>
       </c>
       <c r="D598" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.35">
@@ -9097,7 +9097,7 @@
         <v>46</v>
       </c>
       <c r="D599" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.35">
@@ -9111,7 +9111,7 @@
         <v>48</v>
       </c>
       <c r="D600" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.35">
@@ -9125,7 +9125,7 @@
         <v>50</v>
       </c>
       <c r="D601" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.35">
@@ -9181,7 +9181,7 @@
         <v>6</v>
       </c>
       <c r="D606" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.35">
@@ -9195,7 +9195,7 @@
         <v>8</v>
       </c>
       <c r="D607" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.35">
@@ -9209,7 +9209,7 @@
         <v>10</v>
       </c>
       <c r="D608" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.35">
@@ -9223,7 +9223,7 @@
         <v>12</v>
       </c>
       <c r="D609" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.35">
@@ -9237,7 +9237,7 @@
         <v>14</v>
       </c>
       <c r="D610" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.35">
@@ -9251,7 +9251,7 @@
         <v>16</v>
       </c>
       <c r="D611" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.35">
@@ -9265,7 +9265,7 @@
         <v>18</v>
       </c>
       <c r="D612" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.35">
@@ -9363,7 +9363,7 @@
         <v>32</v>
       </c>
       <c r="D619" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.35">
@@ -9377,7 +9377,7 @@
         <v>34</v>
       </c>
       <c r="D620" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.35">
@@ -9391,7 +9391,7 @@
         <v>36</v>
       </c>
       <c r="D621" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.35">
@@ -9405,7 +9405,7 @@
         <v>38</v>
       </c>
       <c r="D622" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.35">
@@ -9419,7 +9419,7 @@
         <v>40</v>
       </c>
       <c r="D623" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.35">
@@ -9433,7 +9433,7 @@
         <v>42</v>
       </c>
       <c r="D624" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.35">
@@ -9447,7 +9447,7 @@
         <v>44</v>
       </c>
       <c r="D625" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.35">
@@ -9461,7 +9461,7 @@
         <v>46</v>
       </c>
       <c r="D626" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.35">
@@ -9475,7 +9475,7 @@
         <v>48</v>
       </c>
       <c r="D627" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.35">
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="D633" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.35">
@@ -9559,7 +9559,7 @@
         <v>8</v>
       </c>
       <c r="D634" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.35">
@@ -9573,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="D635" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.35">
@@ -9587,7 +9587,7 @@
         <v>12</v>
       </c>
       <c r="D636" t="s">
-        <v>39</v>
+        <v>195</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.35">
@@ -9601,7 +9601,7 @@
         <v>14</v>
       </c>
       <c r="D637" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.35">
@@ -9615,7 +9615,7 @@
         <v>16</v>
       </c>
       <c r="D638" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.35">
@@ -9629,7 +9629,7 @@
         <v>18</v>
       </c>
       <c r="D639" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.35">
@@ -9699,7 +9699,7 @@
         <v>28</v>
       </c>
       <c r="D644" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.35">
@@ -9713,7 +9713,7 @@
         <v>30</v>
       </c>
       <c r="D645" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.35">
@@ -9727,7 +9727,7 @@
         <v>32</v>
       </c>
       <c r="D646" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.35">
@@ -9741,7 +9741,7 @@
         <v>34</v>
       </c>
       <c r="D647" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.35">
@@ -9755,7 +9755,7 @@
         <v>36</v>
       </c>
       <c r="D648" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.35">
@@ -9769,7 +9769,7 @@
         <v>38</v>
       </c>
       <c r="D649" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.35">
@@ -9783,7 +9783,7 @@
         <v>40</v>
       </c>
       <c r="D650" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.35">
@@ -9797,7 +9797,7 @@
         <v>44</v>
       </c>
       <c r="D651" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.35">
@@ -9811,7 +9811,7 @@
         <v>46</v>
       </c>
       <c r="D652" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.35">
@@ -9895,7 +9895,7 @@
         <v>6</v>
       </c>
       <c r="D659" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.35">
@@ -9909,7 +9909,7 @@
         <v>8</v>
       </c>
       <c r="D660" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.35">
@@ -9923,7 +9923,7 @@
         <v>10</v>
       </c>
       <c r="D661" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.35">
@@ -9937,7 +9937,7 @@
         <v>12</v>
       </c>
       <c r="D662" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.35">
@@ -9951,7 +9951,7 @@
         <v>14</v>
       </c>
       <c r="D663" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.35">
@@ -9965,7 +9965,7 @@
         <v>16</v>
       </c>
       <c r="D664" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.35">
@@ -9979,7 +9979,7 @@
         <v>18</v>
       </c>
       <c r="D665" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.35">
@@ -10077,7 +10077,7 @@
         <v>32</v>
       </c>
       <c r="D672" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.35">
@@ -10091,7 +10091,7 @@
         <v>34</v>
       </c>
       <c r="D673" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.35">
@@ -10105,7 +10105,7 @@
         <v>36</v>
       </c>
       <c r="D674" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.35">
@@ -10119,7 +10119,7 @@
         <v>38</v>
       </c>
       <c r="D675" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.35">
@@ -10133,7 +10133,7 @@
         <v>40</v>
       </c>
       <c r="D676" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.35">
@@ -10147,7 +10147,7 @@
         <v>42</v>
       </c>
       <c r="D677" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.35">
@@ -10161,7 +10161,7 @@
         <v>44</v>
       </c>
       <c r="D678" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.35">
@@ -10175,7 +10175,7 @@
         <v>46</v>
       </c>
       <c r="D679" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.35">
@@ -10189,7 +10189,7 @@
         <v>48</v>
       </c>
       <c r="D680" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.35">
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="D686" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.35">
@@ -10273,7 +10273,7 @@
         <v>8</v>
       </c>
       <c r="D687" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.35">
@@ -10287,7 +10287,7 @@
         <v>10</v>
       </c>
       <c r="D688" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.35">
@@ -10301,7 +10301,7 @@
         <v>12</v>
       </c>
       <c r="D689" t="s">
-        <v>102</v>
+        <v>198</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.35">
@@ -10315,7 +10315,7 @@
         <v>14</v>
       </c>
       <c r="D690" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.35">
@@ -10329,7 +10329,7 @@
         <v>16</v>
       </c>
       <c r="D691" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.35">
@@ -10343,7 +10343,7 @@
         <v>18</v>
       </c>
       <c r="D692" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.35">
@@ -10399,7 +10399,7 @@
         <v>26</v>
       </c>
       <c r="D696" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.35">
@@ -10413,7 +10413,7 @@
         <v>28</v>
       </c>
       <c r="D697" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.35">
@@ -10427,7 +10427,7 @@
         <v>30</v>
       </c>
       <c r="D698" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.35">
@@ -10441,7 +10441,7 @@
         <v>32</v>
       </c>
       <c r="D699" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.35">
@@ -10455,7 +10455,7 @@
         <v>34</v>
       </c>
       <c r="D700" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.35">
@@ -10469,7 +10469,7 @@
         <v>36</v>
       </c>
       <c r="D701" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.35">
@@ -10483,7 +10483,7 @@
         <v>38</v>
       </c>
       <c r="D702" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.35">
@@ -10497,7 +10497,7 @@
         <v>42</v>
       </c>
       <c r="D703" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.35">
@@ -10595,7 +10595,7 @@
         <v>6</v>
       </c>
       <c r="D711" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.35">
@@ -10609,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="D712" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.35">
@@ -10623,7 +10623,7 @@
         <v>10</v>
       </c>
       <c r="D713" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.35">
@@ -10637,7 +10637,7 @@
         <v>12</v>
       </c>
       <c r="D714" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.35">
@@ -10651,7 +10651,7 @@
         <v>14</v>
       </c>
       <c r="D715" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.35">
@@ -10665,7 +10665,7 @@
         <v>16</v>
       </c>
       <c r="D716" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.35">
@@ -10679,7 +10679,7 @@
         <v>18</v>
       </c>
       <c r="D717" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.35">
@@ -10735,7 +10735,7 @@
         <v>26</v>
       </c>
       <c r="D721" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.35">
@@ -10749,7 +10749,7 @@
         <v>28</v>
       </c>
       <c r="D722" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.35">
@@ -10763,7 +10763,7 @@
         <v>30</v>
       </c>
       <c r="D723" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.35">
@@ -10777,7 +10777,7 @@
         <v>32</v>
       </c>
       <c r="D724" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.35">
@@ -10791,7 +10791,7 @@
         <v>34</v>
       </c>
       <c r="D725" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.35">
@@ -10805,7 +10805,7 @@
         <v>36</v>
       </c>
       <c r="D726" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.35">
@@ -10819,7 +10819,7 @@
         <v>38</v>
       </c>
       <c r="D727" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.35">
@@ -10833,7 +10833,7 @@
         <v>40</v>
       </c>
       <c r="D728" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.35">
@@ -10847,7 +10847,7 @@
         <v>42</v>
       </c>
       <c r="D729" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.35">
@@ -10861,7 +10861,7 @@
         <v>44</v>
       </c>
       <c r="D730" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.35">
@@ -10959,7 +10959,7 @@
         <v>6</v>
       </c>
       <c r="D738" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.35">
@@ -10973,7 +10973,7 @@
         <v>8</v>
       </c>
       <c r="D739" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.35">
@@ -10987,7 +10987,7 @@
         <v>10</v>
       </c>
       <c r="D740" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.35">
@@ -11001,7 +11001,7 @@
         <v>12</v>
       </c>
       <c r="D741" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.35">
@@ -11015,7 +11015,7 @@
         <v>14</v>
       </c>
       <c r="D742" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.35">
@@ -11029,7 +11029,7 @@
         <v>16</v>
       </c>
       <c r="D743" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.35">
@@ -11043,7 +11043,7 @@
         <v>18</v>
       </c>
       <c r="D744" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.35">
@@ -11113,7 +11113,7 @@
         <v>28</v>
       </c>
       <c r="D749" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.35">
@@ -11127,7 +11127,7 @@
         <v>30</v>
       </c>
       <c r="D750" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.35">
@@ -11141,7 +11141,7 @@
         <v>32</v>
       </c>
       <c r="D751" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.35">
@@ -11155,7 +11155,7 @@
         <v>34</v>
       </c>
       <c r="D752" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.35">
@@ -11169,7 +11169,7 @@
         <v>36</v>
       </c>
       <c r="D753" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.35">
@@ -11183,7 +11183,7 @@
         <v>38</v>
       </c>
       <c r="D754" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.35">
@@ -11197,7 +11197,7 @@
         <v>40</v>
       </c>
       <c r="D755" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.35">
@@ -11211,7 +11211,7 @@
         <v>42</v>
       </c>
       <c r="D756" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.35">
@@ -11323,7 +11323,7 @@
         <v>6</v>
       </c>
       <c r="D765" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.35">
@@ -11337,7 +11337,7 @@
         <v>8</v>
       </c>
       <c r="D766" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.35">
@@ -11351,7 +11351,7 @@
         <v>10</v>
       </c>
       <c r="D767" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.35">
@@ -11365,7 +11365,7 @@
         <v>12</v>
       </c>
       <c r="D768" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.35">
@@ -11379,7 +11379,7 @@
         <v>14</v>
       </c>
       <c r="D769" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.35">
@@ -11393,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="D770" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.35">
@@ -11407,7 +11407,7 @@
         <v>18</v>
       </c>
       <c r="D771" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.35">
@@ -11435,7 +11435,7 @@
         <v>24</v>
       </c>
       <c r="D773" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.35">
@@ -11449,7 +11449,7 @@
         <v>28</v>
       </c>
       <c r="D774" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.35">
@@ -11463,7 +11463,7 @@
         <v>30</v>
       </c>
       <c r="D775" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.35">
@@ -11477,7 +11477,7 @@
         <v>32</v>
       </c>
       <c r="D776" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.35">
@@ -11491,7 +11491,7 @@
         <v>34</v>
       </c>
       <c r="D777" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.35">
@@ -11505,7 +11505,7 @@
         <v>36</v>
       </c>
       <c r="D778" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.35">
@@ -11519,7 +11519,7 @@
         <v>38</v>
       </c>
       <c r="D779" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.35">
@@ -11533,7 +11533,7 @@
         <v>40</v>
       </c>
       <c r="D780" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.35">
@@ -11673,7 +11673,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>11</v>
@@ -11681,7 +11681,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>11</v>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>11</v>
@@ -11705,7 +11705,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>11</v>
@@ -11713,7 +11713,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>11</v>
@@ -11881,7 +11881,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -11889,7 +11889,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -11897,7 +11897,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -11905,7 +11905,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -11913,7 +11913,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -11921,7 +11921,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -11929,7 +11929,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11937,7 +11937,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -11945,7 +11945,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -11953,7 +11953,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -12129,7 +12129,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -12137,7 +12137,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -12145,7 +12145,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -12153,7 +12153,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B62">
         <v>10</v>
@@ -12161,7 +12161,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B64">
         <v>10</v>
@@ -12177,7 +12177,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -12185,7 +12185,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B66">
         <v>10</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B86">
         <v>10</v>
@@ -12353,7 +12353,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B87">
         <v>10</v>

--- a/src/outputs/ta_schedule-final.xlsx
+++ b/src/outputs/ta_schedule-final.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804DF099-600E-4336-97EC-53EA49A689F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="TA Schedule" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sessions Count" state="visible" r:id="rId5"/>
+    <sheet name="TA Schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="Sessions Count" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -638,14 +642,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -668,8 +672,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1008,16 +1015,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D788"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1045,7 +1053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1059,7 +1067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1073,7 +1081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1101,7 +1109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1115,7 +1123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1137,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1143,7 +1151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1157,7 +1165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1171,7 +1179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1185,7 +1193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1199,7 +1207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1213,7 +1221,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1227,7 +1235,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1241,7 +1249,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1269,7 +1277,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1291,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1297,7 +1305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1311,7 +1319,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1333,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1339,7 +1347,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1353,7 +1361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1367,7 +1375,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1389,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1395,7 +1403,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1409,7 +1417,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1423,7 +1431,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1437,7 +1445,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1451,7 +1459,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1465,7 +1473,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1479,7 +1487,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1501,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1521,7 +1529,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1535,7 +1543,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1549,7 +1557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1563,7 +1571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1577,7 +1585,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1591,7 +1599,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1605,7 +1613,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1619,7 +1627,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1633,7 +1641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1647,7 +1655,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1661,7 +1669,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1675,7 +1683,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1689,7 +1697,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1703,7 +1711,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1717,7 +1725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1731,7 +1739,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1745,7 +1753,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1759,7 +1767,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -1773,7 +1781,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1787,7 +1795,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1801,7 +1809,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -1815,7 +1823,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1829,7 +1837,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1843,7 +1851,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -1857,7 +1865,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -1871,7 +1879,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1899,7 +1907,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1913,7 +1921,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1927,7 +1935,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -1941,7 +1949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -1955,7 +1963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -1969,7 +1977,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -1983,7 +1991,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -1997,7 +2005,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2011,7 +2019,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2025,7 +2033,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2039,7 +2047,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2053,7 +2061,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2081,7 +2089,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2095,7 +2103,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2109,7 +2117,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2137,7 +2145,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2151,7 +2159,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2165,7 +2173,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2179,7 +2187,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2193,7 +2201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2207,7 +2215,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2221,7 +2229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2235,7 +2243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2249,7 +2257,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2263,7 +2271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2277,7 +2285,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2291,7 +2299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2305,7 +2313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2319,7 +2327,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2333,7 +2341,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2347,7 +2355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2361,7 +2369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2375,7 +2383,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2389,7 +2397,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2403,7 +2411,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2417,7 +2425,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2431,7 +2439,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2445,7 +2453,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2459,7 +2467,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2473,7 +2481,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2487,7 +2495,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2501,7 +2509,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2515,7 +2523,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -2529,7 +2537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -2543,7 +2551,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -2557,7 +2565,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -2571,7 +2579,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -2585,7 +2593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -2599,7 +2607,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -2613,7 +2621,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -2627,7 +2635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -2641,7 +2649,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -2655,7 +2663,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -2669,7 +2677,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2683,7 +2691,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -2697,7 +2705,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -2711,7 +2719,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -2725,7 +2733,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -2739,7 +2747,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -2753,7 +2761,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -2767,7 +2775,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -2781,7 +2789,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -2795,7 +2803,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -2809,7 +2817,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -2823,7 +2831,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -2837,7 +2845,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -2851,7 +2859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -2865,7 +2873,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2879,7 +2887,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -2893,7 +2901,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -2907,7 +2915,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -2921,7 +2929,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -2935,7 +2943,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -2949,7 +2957,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -2963,7 +2971,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -2977,7 +2985,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -2991,7 +2999,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3005,7 +3013,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3019,7 +3027,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3033,7 +3041,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3047,7 +3055,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3061,7 +3069,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>143</v>
       </c>
@@ -3075,7 +3083,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>143</v>
       </c>
@@ -3089,7 +3097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>143</v>
       </c>
@@ -3103,7 +3111,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>143</v>
       </c>
@@ -3117,7 +3125,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>143</v>
       </c>
@@ -3131,7 +3139,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>143</v>
       </c>
@@ -3145,7 +3153,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>143</v>
       </c>
@@ -3159,7 +3167,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>143</v>
       </c>
@@ -3173,7 +3181,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>143</v>
       </c>
@@ -3187,7 +3195,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>143</v>
       </c>
@@ -3201,7 +3209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>143</v>
       </c>
@@ -3215,7 +3223,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>143</v>
       </c>
@@ -3229,7 +3237,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>143</v>
       </c>
@@ -3243,7 +3251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>143</v>
       </c>
@@ -3257,7 +3265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>143</v>
       </c>
@@ -3271,7 +3279,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>143</v>
       </c>
@@ -3285,7 +3293,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>143</v>
       </c>
@@ -3299,7 +3307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>143</v>
       </c>
@@ -3313,7 +3321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>143</v>
       </c>
@@ -3327,7 +3335,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>143</v>
       </c>
@@ -3341,7 +3349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>143</v>
       </c>
@@ -3355,7 +3363,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>143</v>
       </c>
@@ -3369,7 +3377,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>143</v>
       </c>
@@ -3383,7 +3391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>143</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>143</v>
       </c>
@@ -3411,7 +3419,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>143</v>
       </c>
@@ -3425,7 +3433,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>143</v>
       </c>
@@ -3439,7 +3447,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>143</v>
       </c>
@@ -3453,7 +3461,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>143</v>
       </c>
@@ -3467,7 +3475,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>143</v>
       </c>
@@ -3481,7 +3489,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>143</v>
       </c>
@@ -3495,7 +3503,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>143</v>
       </c>
@@ -3509,7 +3517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>143</v>
       </c>
@@ -3523,7 +3531,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>143</v>
       </c>
@@ -3537,7 +3545,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>143</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>143</v>
       </c>
@@ -3565,7 +3573,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>143</v>
       </c>
@@ -3579,7 +3587,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>143</v>
       </c>
@@ -3593,7 +3601,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>143</v>
       </c>
@@ -3607,7 +3615,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>143</v>
       </c>
@@ -3621,7 +3629,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>143</v>
       </c>
@@ -3635,7 +3643,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>143</v>
       </c>
@@ -3649,7 +3657,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>143</v>
       </c>
@@ -3663,7 +3671,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>143</v>
       </c>
@@ -3677,7 +3685,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>143</v>
       </c>
@@ -3691,7 +3699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>143</v>
       </c>
@@ -3705,7 +3713,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>143</v>
       </c>
@@ -3719,7 +3727,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>143</v>
       </c>
@@ -3733,7 +3741,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>143</v>
       </c>
@@ -3747,7 +3755,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>143</v>
       </c>
@@ -3761,7 +3769,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>143</v>
       </c>
@@ -3775,7 +3783,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>143</v>
       </c>
@@ -3789,7 +3797,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>143</v>
       </c>
@@ -3803,7 +3811,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>143</v>
       </c>
@@ -3817,7 +3825,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>143</v>
       </c>
@@ -3831,7 +3839,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>143</v>
       </c>
@@ -3845,7 +3853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>143</v>
       </c>
@@ -3859,7 +3867,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>143</v>
       </c>
@@ -3873,7 +3881,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>143</v>
       </c>
@@ -3887,7 +3895,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>143</v>
       </c>
@@ -3901,7 +3909,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>143</v>
       </c>
@@ -3915,7 +3923,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>143</v>
       </c>
@@ -3929,7 +3937,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>143</v>
       </c>
@@ -3943,7 +3951,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>143</v>
       </c>
@@ -3957,7 +3965,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>143</v>
       </c>
@@ -3971,7 +3979,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>143</v>
       </c>
@@ -3985,7 +3993,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>143</v>
       </c>
@@ -3999,7 +4007,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>143</v>
       </c>
@@ -4013,7 +4021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>143</v>
       </c>
@@ -4027,7 +4035,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>143</v>
       </c>
@@ -4041,7 +4049,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>143</v>
       </c>
@@ -4055,7 +4063,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>143</v>
       </c>
@@ -4069,7 +4077,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>143</v>
       </c>
@@ -4083,7 +4091,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>143</v>
       </c>
@@ -4097,7 +4105,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>143</v>
       </c>
@@ -4111,7 +4119,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>143</v>
       </c>
@@ -4125,7 +4133,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>143</v>
       </c>
@@ -4139,7 +4147,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>143</v>
       </c>
@@ -4153,7 +4161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -4167,7 +4175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>143</v>
       </c>
@@ -4181,7 +4189,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>143</v>
       </c>
@@ -4195,7 +4203,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>143</v>
       </c>
@@ -4209,7 +4217,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>143</v>
       </c>
@@ -4223,7 +4231,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>143</v>
       </c>
@@ -4237,7 +4245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>143</v>
       </c>
@@ -4251,7 +4259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>143</v>
       </c>
@@ -4265,7 +4273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>143</v>
       </c>
@@ -4279,7 +4287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>143</v>
       </c>
@@ -4293,7 +4301,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>143</v>
       </c>
@@ -4307,7 +4315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>143</v>
       </c>
@@ -4321,7 +4329,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>143</v>
       </c>
@@ -4335,7 +4343,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>143</v>
       </c>
@@ -4349,7 +4357,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>143</v>
       </c>
@@ -4363,7 +4371,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>143</v>
       </c>
@@ -4377,7 +4385,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>143</v>
       </c>
@@ -4391,7 +4399,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>143</v>
       </c>
@@ -4405,7 +4413,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>143</v>
       </c>
@@ -4419,7 +4427,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>143</v>
       </c>
@@ -4433,7 +4441,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>143</v>
       </c>
@@ -4447,7 +4455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>143</v>
       </c>
@@ -4461,7 +4469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>143</v>
       </c>
@@ -4475,7 +4483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>143</v>
       </c>
@@ -4489,7 +4497,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>143</v>
       </c>
@@ -4503,7 +4511,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>143</v>
       </c>
@@ -4517,7 +4525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>143</v>
       </c>
@@ -4531,7 +4539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>143</v>
       </c>
@@ -4545,7 +4553,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>143</v>
       </c>
@@ -4559,7 +4567,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>143</v>
       </c>
@@ -4573,7 +4581,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>143</v>
       </c>
@@ -4587,7 +4595,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>143</v>
       </c>
@@ -4601,7 +4609,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>143</v>
       </c>
@@ -4615,7 +4623,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>143</v>
       </c>
@@ -4629,7 +4637,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>143</v>
       </c>
@@ -4643,7 +4651,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>143</v>
       </c>
@@ -4657,7 +4665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>143</v>
       </c>
@@ -4671,7 +4679,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>143</v>
       </c>
@@ -4685,7 +4693,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>143</v>
       </c>
@@ -4699,7 +4707,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>143</v>
       </c>
@@ -4713,7 +4721,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>143</v>
       </c>
@@ -4727,7 +4735,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>143</v>
       </c>
@@ -4741,7 +4749,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>143</v>
       </c>
@@ -4755,7 +4763,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>143</v>
       </c>
@@ -4769,7 +4777,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>143</v>
       </c>
@@ -4783,7 +4791,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>143</v>
       </c>
@@ -4797,7 +4805,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>143</v>
       </c>
@@ -4811,7 +4819,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>143</v>
       </c>
@@ -4825,7 +4833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>143</v>
       </c>
@@ -4839,7 +4847,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>143</v>
       </c>
@@ -4853,7 +4861,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>143</v>
       </c>
@@ -4867,7 +4875,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>143</v>
       </c>
@@ -4881,7 +4889,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>143</v>
       </c>
@@ -4895,7 +4903,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>143</v>
       </c>
@@ -4909,7 +4917,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>143</v>
       </c>
@@ -4923,7 +4931,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>143</v>
       </c>
@@ -4937,7 +4945,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>143</v>
       </c>
@@ -4951,7 +4959,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>143</v>
       </c>
@@ -4965,7 +4973,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>143</v>
       </c>
@@ -4979,7 +4987,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>143</v>
       </c>
@@ -4993,7 +5001,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>143</v>
       </c>
@@ -5007,7 +5015,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>143</v>
       </c>
@@ -5021,7 +5029,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>143</v>
       </c>
@@ -5035,7 +5043,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>143</v>
       </c>
@@ -5049,7 +5057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>143</v>
       </c>
@@ -5063,7 +5071,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>143</v>
       </c>
@@ -5077,7 +5085,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>143</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>143</v>
       </c>
@@ -5105,7 +5113,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>143</v>
       </c>
@@ -5119,7 +5127,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>143</v>
       </c>
@@ -5133,7 +5141,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>143</v>
       </c>
@@ -5147,7 +5155,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>143</v>
       </c>
@@ -5161,7 +5169,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>143</v>
       </c>
@@ -5175,7 +5183,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>143</v>
       </c>
@@ -5189,7 +5197,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>143</v>
       </c>
@@ -5203,7 +5211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>143</v>
       </c>
@@ -5217,7 +5225,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>143</v>
       </c>
@@ -5231,7 +5239,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>172</v>
       </c>
@@ -5245,7 +5253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>172</v>
       </c>
@@ -5259,7 +5267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>172</v>
       </c>
@@ -5273,7 +5281,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>172</v>
       </c>
@@ -5287,7 +5295,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>172</v>
       </c>
@@ -5301,7 +5309,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>172</v>
       </c>
@@ -5315,7 +5323,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>172</v>
       </c>
@@ -5329,7 +5337,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>172</v>
       </c>
@@ -5343,7 +5351,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>172</v>
       </c>
@@ -5357,7 +5365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>172</v>
       </c>
@@ -5371,7 +5379,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>172</v>
       </c>
@@ -5385,7 +5393,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>172</v>
       </c>
@@ -5399,7 +5407,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>172</v>
       </c>
@@ -5413,7 +5421,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>172</v>
       </c>
@@ -5427,7 +5435,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>172</v>
       </c>
@@ -5441,7 +5449,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>172</v>
       </c>
@@ -5455,7 +5463,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>172</v>
       </c>
@@ -5469,7 +5477,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>172</v>
       </c>
@@ -5483,7 +5491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>172</v>
       </c>
@@ -5497,7 +5505,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>172</v>
       </c>
@@ -5511,7 +5519,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>172</v>
       </c>
@@ -5525,7 +5533,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>172</v>
       </c>
@@ -5539,7 +5547,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>172</v>
       </c>
@@ -5553,7 +5561,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>172</v>
       </c>
@@ -5567,7 +5575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>172</v>
       </c>
@@ -5581,7 +5589,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>172</v>
       </c>
@@ -5595,7 +5603,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>172</v>
       </c>
@@ -5609,7 +5617,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>172</v>
       </c>
@@ -5623,7 +5631,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>172</v>
       </c>
@@ -5637,7 +5645,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>172</v>
       </c>
@@ -5651,7 +5659,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>172</v>
       </c>
@@ -5665,7 +5673,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>172</v>
       </c>
@@ -5679,7 +5687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>172</v>
       </c>
@@ -5693,7 +5701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>172</v>
       </c>
@@ -5707,7 +5715,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>172</v>
       </c>
@@ -5721,7 +5729,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>172</v>
       </c>
@@ -5735,7 +5743,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>172</v>
       </c>
@@ -5749,7 +5757,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>172</v>
       </c>
@@ -5763,7 +5771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>172</v>
       </c>
@@ -5777,7 +5785,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>172</v>
       </c>
@@ -5791,7 +5799,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>172</v>
       </c>
@@ -5805,7 +5813,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>172</v>
       </c>
@@ -5819,7 +5827,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>172</v>
       </c>
@@ -5833,7 +5841,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>172</v>
       </c>
@@ -5847,7 +5855,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>172</v>
       </c>
@@ -5861,7 +5869,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>172</v>
       </c>
@@ -5875,7 +5883,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>172</v>
       </c>
@@ -5889,7 +5897,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>172</v>
       </c>
@@ -5903,7 +5911,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>172</v>
       </c>
@@ -5917,7 +5925,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>172</v>
       </c>
@@ -5931,7 +5939,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>172</v>
       </c>
@@ -5945,7 +5953,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>172</v>
       </c>
@@ -5959,7 +5967,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>172</v>
       </c>
@@ -5973,7 +5981,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>172</v>
       </c>
@@ -5987,7 +5995,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>172</v>
       </c>
@@ -6001,7 +6009,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>172</v>
       </c>
@@ -6015,7 +6023,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>172</v>
       </c>
@@ -6029,7 +6037,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>172</v>
       </c>
@@ -6043,7 +6051,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>172</v>
       </c>
@@ -6057,7 +6065,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>172</v>
       </c>
@@ -6071,7 +6079,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>172</v>
       </c>
@@ -6085,7 +6093,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>172</v>
       </c>
@@ -6099,7 +6107,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>172</v>
       </c>
@@ -6113,7 +6121,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>172</v>
       </c>
@@ -6127,7 +6135,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>172</v>
       </c>
@@ -6141,7 +6149,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>172</v>
       </c>
@@ -6155,7 +6163,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>172</v>
       </c>
@@ -6169,7 +6177,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>172</v>
       </c>
@@ -6183,7 +6191,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>172</v>
       </c>
@@ -6197,7 +6205,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>172</v>
       </c>
@@ -6211,7 +6219,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>172</v>
       </c>
@@ -6225,7 +6233,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>172</v>
       </c>
@@ -6239,7 +6247,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>172</v>
       </c>
@@ -6253,7 +6261,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>172</v>
       </c>
@@ -6267,7 +6275,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>172</v>
       </c>
@@ -6281,7 +6289,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>172</v>
       </c>
@@ -6295,7 +6303,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>172</v>
       </c>
@@ -6309,7 +6317,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>172</v>
       </c>
@@ -6323,7 +6331,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>172</v>
       </c>
@@ -6337,7 +6345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>172</v>
       </c>
@@ -6351,7 +6359,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>172</v>
       </c>
@@ -6365,7 +6373,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>172</v>
       </c>
@@ -6379,7 +6387,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>172</v>
       </c>
@@ -6393,7 +6401,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>172</v>
       </c>
@@ -6407,7 +6415,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>172</v>
       </c>
@@ -6421,7 +6429,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>172</v>
       </c>
@@ -6435,7 +6443,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>172</v>
       </c>
@@ -6449,7 +6457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>172</v>
       </c>
@@ -6463,7 +6471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>172</v>
       </c>
@@ -6477,7 +6485,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>172</v>
       </c>
@@ -6491,7 +6499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>172</v>
       </c>
@@ -6505,7 +6513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>172</v>
       </c>
@@ -6519,7 +6527,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>172</v>
       </c>
@@ -6533,7 +6541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>172</v>
       </c>
@@ -6547,7 +6555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>172</v>
       </c>
@@ -6561,7 +6569,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>172</v>
       </c>
@@ -6575,7 +6583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>172</v>
       </c>
@@ -6589,7 +6597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>172</v>
       </c>
@@ -6603,7 +6611,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>172</v>
       </c>
@@ -6617,7 +6625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>172</v>
       </c>
@@ -6631,7 +6639,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>172</v>
       </c>
@@ -6645,7 +6653,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>172</v>
       </c>
@@ -6659,7 +6667,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>172</v>
       </c>
@@ -6673,7 +6681,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>172</v>
       </c>
@@ -6687,7 +6695,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>172</v>
       </c>
@@ -6701,7 +6709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>172</v>
       </c>
@@ -6715,7 +6723,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>172</v>
       </c>
@@ -6729,7 +6737,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>172</v>
       </c>
@@ -6743,7 +6751,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>172</v>
       </c>
@@ -6757,7 +6765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>172</v>
       </c>
@@ -6771,7 +6779,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>172</v>
       </c>
@@ -6785,7 +6793,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>172</v>
       </c>
@@ -6799,7 +6807,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>172</v>
       </c>
@@ -6813,7 +6821,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>172</v>
       </c>
@@ -6827,7 +6835,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>172</v>
       </c>
@@ -6841,7 +6849,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>172</v>
       </c>
@@ -6855,7 +6863,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>172</v>
       </c>
@@ -6869,7 +6877,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>172</v>
       </c>
@@ -6883,7 +6891,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>172</v>
       </c>
@@ -6897,7 +6905,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>172</v>
       </c>
@@ -6911,7 +6919,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>172</v>
       </c>
@@ -6925,7 +6933,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>172</v>
       </c>
@@ -6939,7 +6947,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>172</v>
       </c>
@@ -6953,7 +6961,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>172</v>
       </c>
@@ -6967,7 +6975,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>172</v>
       </c>
@@ -6981,7 +6989,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>172</v>
       </c>
@@ -6995,7 +7003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>172</v>
       </c>
@@ -7009,7 +7017,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>172</v>
       </c>
@@ -7023,7 +7031,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>172</v>
       </c>
@@ -7037,7 +7045,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>172</v>
       </c>
@@ -7051,7 +7059,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>172</v>
       </c>
@@ -7065,7 +7073,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>172</v>
       </c>
@@ -7079,7 +7087,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>172</v>
       </c>
@@ -7093,7 +7101,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>172</v>
       </c>
@@ -7107,7 +7115,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>172</v>
       </c>
@@ -7121,7 +7129,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>172</v>
       </c>
@@ -7135,7 +7143,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>172</v>
       </c>
@@ -7149,7 +7157,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>172</v>
       </c>
@@ -7163,7 +7171,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>172</v>
       </c>
@@ -7177,7 +7185,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>172</v>
       </c>
@@ -7191,7 +7199,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>172</v>
       </c>
@@ -7205,7 +7213,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>172</v>
       </c>
@@ -7219,7 +7227,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>172</v>
       </c>
@@ -7233,7 +7241,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>172</v>
       </c>
@@ -7247,7 +7255,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>172</v>
       </c>
@@ -7261,7 +7269,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>172</v>
       </c>
@@ -7275,7 +7283,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>172</v>
       </c>
@@ -7289,7 +7297,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>172</v>
       </c>
@@ -7303,7 +7311,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>172</v>
       </c>
@@ -7317,7 +7325,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>172</v>
       </c>
@@ -7331,7 +7339,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>172</v>
       </c>
@@ -7345,7 +7353,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>188</v>
       </c>
@@ -7359,7 +7367,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>188</v>
       </c>
@@ -7373,7 +7381,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>188</v>
       </c>
@@ -7387,7 +7395,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>188</v>
       </c>
@@ -7401,7 +7409,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>188</v>
       </c>
@@ -7415,7 +7423,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>188</v>
       </c>
@@ -7429,7 +7437,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>188</v>
       </c>
@@ -7443,7 +7451,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>188</v>
       </c>
@@ -7457,7 +7465,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>188</v>
       </c>
@@ -7471,7 +7479,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>188</v>
       </c>
@@ -7485,7 +7493,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>188</v>
       </c>
@@ -7499,7 +7507,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>188</v>
       </c>
@@ -7513,7 +7521,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>188</v>
       </c>
@@ -7527,7 +7535,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>188</v>
       </c>
@@ -7541,7 +7549,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>188</v>
       </c>
@@ -7555,7 +7563,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>188</v>
       </c>
@@ -7569,7 +7577,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>188</v>
       </c>
@@ -7583,7 +7591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>188</v>
       </c>
@@ -7597,7 +7605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>188</v>
       </c>
@@ -7611,7 +7619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>188</v>
       </c>
@@ -7625,7 +7633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>188</v>
       </c>
@@ -7639,7 +7647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>188</v>
       </c>
@@ -7653,7 +7661,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>188</v>
       </c>
@@ -7667,7 +7675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>188</v>
       </c>
@@ -7681,7 +7689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>188</v>
       </c>
@@ -7695,7 +7703,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>188</v>
       </c>
@@ -7709,7 +7717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>188</v>
       </c>
@@ -7723,7 +7731,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>188</v>
       </c>
@@ -7737,7 +7745,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>188</v>
       </c>
@@ -7751,7 +7759,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>188</v>
       </c>
@@ -7765,7 +7773,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>188</v>
       </c>
@@ -7779,7 +7787,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>188</v>
       </c>
@@ -7793,7 +7801,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>188</v>
       </c>
@@ -7807,7 +7815,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>188</v>
       </c>
@@ -7821,7 +7829,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>188</v>
       </c>
@@ -7835,7 +7843,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>188</v>
       </c>
@@ -7849,7 +7857,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>188</v>
       </c>
@@ -7863,7 +7871,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>188</v>
       </c>
@@ -7877,7 +7885,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>188</v>
       </c>
@@ -7891,7 +7899,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>188</v>
       </c>
@@ -7905,7 +7913,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>188</v>
       </c>
@@ -7919,7 +7927,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>188</v>
       </c>
@@ -7933,7 +7941,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>188</v>
       </c>
@@ -7947,7 +7955,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>188</v>
       </c>
@@ -7961,7 +7969,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>188</v>
       </c>
@@ -7975,7 +7983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>188</v>
       </c>
@@ -7989,7 +7997,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>188</v>
       </c>
@@ -8003,7 +8011,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>188</v>
       </c>
@@ -8017,7 +8025,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>188</v>
       </c>
@@ -8031,7 +8039,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>188</v>
       </c>
@@ -8045,7 +8053,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>188</v>
       </c>
@@ -8059,7 +8067,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>188</v>
       </c>
@@ -8073,7 +8081,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>188</v>
       </c>
@@ -8087,7 +8095,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>188</v>
       </c>
@@ -8101,7 +8109,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>188</v>
       </c>
@@ -8115,7 +8123,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>188</v>
       </c>
@@ -8129,7 +8137,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>188</v>
       </c>
@@ -8143,7 +8151,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>188</v>
       </c>
@@ -8157,7 +8165,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>188</v>
       </c>
@@ -8171,7 +8179,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>188</v>
       </c>
@@ -8185,7 +8193,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>188</v>
       </c>
@@ -8199,7 +8207,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>188</v>
       </c>
@@ -8213,7 +8221,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>188</v>
       </c>
@@ -8227,7 +8235,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>188</v>
       </c>
@@ -8241,7 +8249,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>188</v>
       </c>
@@ -8255,7 +8263,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>188</v>
       </c>
@@ -8269,7 +8277,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>188</v>
       </c>
@@ -8283,7 +8291,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>188</v>
       </c>
@@ -8297,7 +8305,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>188</v>
       </c>
@@ -8311,7 +8319,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>188</v>
       </c>
@@ -8325,7 +8333,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>188</v>
       </c>
@@ -8339,7 +8347,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>188</v>
       </c>
@@ -8353,7 +8361,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>188</v>
       </c>
@@ -8367,7 +8375,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>188</v>
       </c>
@@ -8381,7 +8389,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>188</v>
       </c>
@@ -8395,7 +8403,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>188</v>
       </c>
@@ -8409,7 +8417,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>188</v>
       </c>
@@ -8423,7 +8431,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>188</v>
       </c>
@@ -8437,7 +8445,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>188</v>
       </c>
@@ -8451,7 +8459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>188</v>
       </c>
@@ -8465,7 +8473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>188</v>
       </c>
@@ -8479,7 +8487,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>188</v>
       </c>
@@ -8493,7 +8501,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>188</v>
       </c>
@@ -8507,7 +8515,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>188</v>
       </c>
@@ -8521,7 +8529,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>188</v>
       </c>
@@ -8535,7 +8543,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>188</v>
       </c>
@@ -8549,7 +8557,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>188</v>
       </c>
@@ -8563,7 +8571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>188</v>
       </c>
@@ -8577,7 +8585,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>188</v>
       </c>
@@ -8591,7 +8599,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>188</v>
       </c>
@@ -8605,7 +8613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>188</v>
       </c>
@@ -8619,7 +8627,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>188</v>
       </c>
@@ -8633,7 +8641,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>188</v>
       </c>
@@ -8647,7 +8655,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>188</v>
       </c>
@@ -8661,7 +8669,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>188</v>
       </c>
@@ -8675,7 +8683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>188</v>
       </c>
@@ -8689,7 +8697,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>188</v>
       </c>
@@ -8703,7 +8711,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>188</v>
       </c>
@@ -8717,7 +8725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>188</v>
       </c>
@@ -8731,7 +8739,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>188</v>
       </c>
@@ -8745,7 +8753,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>188</v>
       </c>
@@ -8759,7 +8767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>188</v>
       </c>
@@ -8773,7 +8781,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>188</v>
       </c>
@@ -8787,7 +8795,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>188</v>
       </c>
@@ -8801,7 +8809,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>188</v>
       </c>
@@ -8815,7 +8823,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>188</v>
       </c>
@@ -8829,7 +8837,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>188</v>
       </c>
@@ -8843,7 +8851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>188</v>
       </c>
@@ -8857,7 +8865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>188</v>
       </c>
@@ -8871,7 +8879,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>188</v>
       </c>
@@ -8885,7 +8893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>188</v>
       </c>
@@ -8899,7 +8907,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>188</v>
       </c>
@@ -8913,7 +8921,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>188</v>
       </c>
@@ -8927,7 +8935,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>188</v>
       </c>
@@ -8941,7 +8949,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>188</v>
       </c>
@@ -8955,7 +8963,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>188</v>
       </c>
@@ -8969,7 +8977,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>188</v>
       </c>
@@ -8983,7 +8991,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>188</v>
       </c>
@@ -8997,7 +9005,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>188</v>
       </c>
@@ -9011,7 +9019,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>188</v>
       </c>
@@ -9025,7 +9033,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>188</v>
       </c>
@@ -9039,7 +9047,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>188</v>
       </c>
@@ -9053,7 +9061,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>188</v>
       </c>
@@ -9067,7 +9075,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>188</v>
       </c>
@@ -9081,7 +9089,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>188</v>
       </c>
@@ -9095,7 +9103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>188</v>
       </c>
@@ -9109,7 +9117,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>188</v>
       </c>
@@ -9123,7 +9131,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>188</v>
       </c>
@@ -9137,7 +9145,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>188</v>
       </c>
@@ -9151,7 +9159,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>188</v>
       </c>
@@ -9165,7 +9173,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>188</v>
       </c>
@@ -9179,7 +9187,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>188</v>
       </c>
@@ -9193,7 +9201,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>188</v>
       </c>
@@ -9207,7 +9215,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>188</v>
       </c>
@@ -9221,7 +9229,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>188</v>
       </c>
@@ -9235,7 +9243,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>188</v>
       </c>
@@ -9249,7 +9257,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>188</v>
       </c>
@@ -9263,7 +9271,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>188</v>
       </c>
@@ -9277,7 +9285,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>188</v>
       </c>
@@ -9291,7 +9299,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>188</v>
       </c>
@@ -9305,7 +9313,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>188</v>
       </c>
@@ -9319,7 +9327,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>188</v>
       </c>
@@ -9333,7 +9341,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>188</v>
       </c>
@@ -9347,7 +9355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>188</v>
       </c>
@@ -9361,7 +9369,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>188</v>
       </c>
@@ -9375,7 +9383,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>188</v>
       </c>
@@ -9389,7 +9397,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>188</v>
       </c>
@@ -9403,7 +9411,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>188</v>
       </c>
@@ -9417,7 +9425,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>188</v>
       </c>
@@ -9431,7 +9439,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>188</v>
       </c>
@@ -9445,7 +9453,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>188</v>
       </c>
@@ -9459,7 +9467,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>188</v>
       </c>
@@ -9473,7 +9481,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>188</v>
       </c>
@@ -9487,7 +9495,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>188</v>
       </c>
@@ -9501,7 +9509,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>188</v>
       </c>
@@ -9515,7 +9523,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>188</v>
       </c>
@@ -9529,7 +9537,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>197</v>
       </c>
@@ -9543,7 +9551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>197</v>
       </c>
@@ -9557,7 +9565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>197</v>
       </c>
@@ -9571,7 +9579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>197</v>
       </c>
@@ -9585,7 +9593,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>197</v>
       </c>
@@ -9599,7 +9607,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>197</v>
       </c>
@@ -9613,7 +9621,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>197</v>
       </c>
@@ -9627,7 +9635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>197</v>
       </c>
@@ -9641,7 +9649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>197</v>
       </c>
@@ -9655,7 +9663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>197</v>
       </c>
@@ -9669,7 +9677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>197</v>
       </c>
@@ -9683,7 +9691,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>197</v>
       </c>
@@ -9697,7 +9705,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>197</v>
       </c>
@@ -9711,7 +9719,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>197</v>
       </c>
@@ -9725,7 +9733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>197</v>
       </c>
@@ -9739,7 +9747,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>197</v>
       </c>
@@ -9753,7 +9761,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>197</v>
       </c>
@@ -9767,7 +9775,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>197</v>
       </c>
@@ -9781,7 +9789,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>197</v>
       </c>
@@ -9795,7 +9803,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>197</v>
       </c>
@@ -9809,7 +9817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>197</v>
       </c>
@@ -9823,7 +9831,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>197</v>
       </c>
@@ -9837,7 +9845,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>197</v>
       </c>
@@ -9851,7 +9859,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>197</v>
       </c>
@@ -9865,7 +9873,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>197</v>
       </c>
@@ -9879,7 +9887,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>197</v>
       </c>
@@ -9893,7 +9901,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>197</v>
       </c>
@@ -9907,7 +9915,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>197</v>
       </c>
@@ -9921,7 +9929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>197</v>
       </c>
@@ -9935,7 +9943,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>197</v>
       </c>
@@ -9949,7 +9957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>197</v>
       </c>
@@ -9963,7 +9971,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>197</v>
       </c>
@@ -9977,7 +9985,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>197</v>
       </c>
@@ -9991,7 +9999,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>197</v>
       </c>
@@ -10005,7 +10013,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>197</v>
       </c>
@@ -10019,7 +10027,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>197</v>
       </c>
@@ -10033,7 +10041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>197</v>
       </c>
@@ -10047,7 +10055,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>197</v>
       </c>
@@ -10061,7 +10069,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>197</v>
       </c>
@@ -10075,7 +10083,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>197</v>
       </c>
@@ -10089,7 +10097,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>197</v>
       </c>
@@ -10103,7 +10111,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>197</v>
       </c>
@@ -10117,7 +10125,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>197</v>
       </c>
@@ -10131,7 +10139,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>197</v>
       </c>
@@ -10145,7 +10153,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>197</v>
       </c>
@@ -10159,7 +10167,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>197</v>
       </c>
@@ -10173,7 +10181,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>197</v>
       </c>
@@ -10187,7 +10195,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>197</v>
       </c>
@@ -10201,7 +10209,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>197</v>
       </c>
@@ -10215,7 +10223,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>197</v>
       </c>
@@ -10229,7 +10237,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>197</v>
       </c>
@@ -10243,7 +10251,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>197</v>
       </c>
@@ -10257,7 +10265,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>197</v>
       </c>
@@ -10271,7 +10279,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>197</v>
       </c>
@@ -10285,7 +10293,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>197</v>
       </c>
@@ -10299,7 +10307,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>197</v>
       </c>
@@ -10313,7 +10321,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>197</v>
       </c>
@@ -10327,7 +10335,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>197</v>
       </c>
@@ -10341,7 +10349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>197</v>
       </c>
@@ -10355,7 +10363,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>197</v>
       </c>
@@ -10369,7 +10377,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>197</v>
       </c>
@@ -10383,7 +10391,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>197</v>
       </c>
@@ -10397,7 +10405,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>197</v>
       </c>
@@ -10411,7 +10419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>197</v>
       </c>
@@ -10425,7 +10433,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>197</v>
       </c>
@@ -10439,7 +10447,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>197</v>
       </c>
@@ -10453,7 +10461,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>197</v>
       </c>
@@ -10467,7 +10475,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>197</v>
       </c>
@@ -10481,7 +10489,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>197</v>
       </c>
@@ -10495,7 +10503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>197</v>
       </c>
@@ -10509,7 +10517,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>197</v>
       </c>
@@ -10523,7 +10531,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>197</v>
       </c>
@@ -10537,7 +10545,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>197</v>
       </c>
@@ -10551,7 +10559,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>197</v>
       </c>
@@ -10565,7 +10573,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>197</v>
       </c>
@@ -10579,7 +10587,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>197</v>
       </c>
@@ -10593,7 +10601,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>197</v>
       </c>
@@ -10607,7 +10615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>197</v>
       </c>
@@ -10621,7 +10629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>197</v>
       </c>
@@ -10635,7 +10643,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>197</v>
       </c>
@@ -10649,7 +10657,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>197</v>
       </c>
@@ -10663,7 +10671,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>197</v>
       </c>
@@ -10677,7 +10685,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>197</v>
       </c>
@@ -10691,7 +10699,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>197</v>
       </c>
@@ -10705,7 +10713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>197</v>
       </c>
@@ -10719,7 +10727,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>197</v>
       </c>
@@ -10733,7 +10741,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>197</v>
       </c>
@@ -10747,7 +10755,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>197</v>
       </c>
@@ -10761,7 +10769,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>197</v>
       </c>
@@ -10775,7 +10783,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>197</v>
       </c>
@@ -10789,7 +10797,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>197</v>
       </c>
@@ -10803,7 +10811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>197</v>
       </c>
@@ -10817,7 +10825,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>197</v>
       </c>
@@ -10831,7 +10839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>197</v>
       </c>
@@ -10845,7 +10853,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>197</v>
       </c>
@@ -10859,7 +10867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>197</v>
       </c>
@@ -10873,7 +10881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>197</v>
       </c>
@@ -10887,7 +10895,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>197</v>
       </c>
@@ -10901,7 +10909,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>197</v>
       </c>
@@ -10915,7 +10923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>197</v>
       </c>
@@ -10929,7 +10937,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>197</v>
       </c>
@@ -10943,7 +10951,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>197</v>
       </c>
@@ -10957,7 +10965,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>197</v>
       </c>
@@ -10971,7 +10979,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>197</v>
       </c>
@@ -10985,7 +10993,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>197</v>
       </c>
@@ -10999,7 +11007,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>197</v>
       </c>
@@ -11013,7 +11021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>197</v>
       </c>
@@ -11027,7 +11035,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>197</v>
       </c>
@@ -11041,7 +11049,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>197</v>
       </c>
@@ -11055,7 +11063,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>197</v>
       </c>
@@ -11069,7 +11077,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>197</v>
       </c>
@@ -11083,7 +11091,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>197</v>
       </c>
@@ -11097,7 +11105,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>197</v>
       </c>
@@ -11111,7 +11119,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>197</v>
       </c>
@@ -11125,7 +11133,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>197</v>
       </c>
@@ -11139,7 +11147,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>197</v>
       </c>
@@ -11153,7 +11161,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>197</v>
       </c>
@@ -11167,7 +11175,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>197</v>
       </c>
@@ -11181,7 +11189,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>197</v>
       </c>
@@ -11195,7 +11203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>197</v>
       </c>
@@ -11209,7 +11217,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>197</v>
       </c>
@@ -11223,7 +11231,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>197</v>
       </c>
@@ -11237,7 +11245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
         <v>197</v>
       </c>
@@ -11251,7 +11259,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>197</v>
       </c>
@@ -11265,7 +11273,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>197</v>
       </c>
@@ -11279,7 +11287,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>197</v>
       </c>
@@ -11293,7 +11301,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>197</v>
       </c>
@@ -11307,7 +11315,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>197</v>
       </c>
@@ -11321,7 +11329,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>197</v>
       </c>
@@ -11335,7 +11343,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>197</v>
       </c>
@@ -11349,7 +11357,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>197</v>
       </c>
@@ -11363,7 +11371,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>197</v>
       </c>
@@ -11377,7 +11385,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>197</v>
       </c>
@@ -11391,7 +11399,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>197</v>
       </c>
@@ -11405,7 +11413,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>197</v>
       </c>
@@ -11419,7 +11427,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>197</v>
       </c>
@@ -11433,7 +11441,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>197</v>
       </c>
@@ -11447,7 +11455,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>197</v>
       </c>
@@ -11461,7 +11469,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>197</v>
       </c>
@@ -11475,7 +11483,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
         <v>197</v>
       </c>
@@ -11489,7 +11497,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>197</v>
       </c>
@@ -11503,7 +11511,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>197</v>
       </c>
@@ -11517,7 +11525,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>197</v>
       </c>
@@ -11531,7 +11539,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="781" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
         <v>197</v>
       </c>
@@ -11545,7 +11553,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A782" t="s">
         <v>197</v>
       </c>
@@ -11559,7 +11567,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
         <v>197</v>
       </c>
@@ -11573,7 +11581,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
         <v>197</v>
       </c>
@@ -11587,7 +11595,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
         <v>197</v>
       </c>
@@ -11601,7 +11609,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
         <v>197</v>
       </c>
@@ -11615,7 +11623,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
         <v>197</v>
       </c>
@@ -11629,7 +11637,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
         <v>197</v>
       </c>
@@ -11645,733 +11653,733 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="40" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="1">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/src/outputs/ta_schedule-final.xlsx
+++ b/src/outputs/ta_schedule-final.xlsx
@@ -1,15 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52446EE7-2610-48D9-8604-02682F0D0AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="TA Schedule" sheetId="1" r:id="rId1"/>
-    <sheet name="Sessions Count" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="TA Schedule" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sessions Count" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -612,14 +608,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -982,17 +978,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D790"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1034,7 +1029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1048,7 +1043,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1062,7 +1057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1090,7 +1085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1132,7 +1127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1160,7 +1155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1174,7 +1169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1188,7 +1183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1202,7 +1197,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1216,7 +1211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1230,7 +1225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1239,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1253,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1272,7 +1267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1286,7 +1281,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1300,7 +1295,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1309,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1323,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1342,7 +1337,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1356,7 +1351,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1370,7 +1365,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1384,7 +1379,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1398,7 +1393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1412,7 +1407,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1426,7 +1421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1440,7 +1435,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1449,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1468,7 +1463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1482,7 +1477,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1496,7 +1491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1510,7 +1505,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1524,7 +1519,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1538,7 +1533,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1552,7 +1547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1566,7 +1561,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1580,7 +1575,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1594,7 +1589,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1608,7 +1603,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1622,7 +1617,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1636,7 +1631,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1650,7 +1645,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1664,7 +1659,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1678,7 +1673,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1692,7 +1687,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1706,7 +1701,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1720,7 +1715,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1734,7 +1729,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1748,7 +1743,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1762,7 +1757,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1776,7 +1771,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -1790,7 +1785,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1804,7 +1799,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1818,7 +1813,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -1832,7 +1827,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -1846,7 +1841,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -1860,7 +1855,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1874,7 +1869,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1888,7 +1883,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1902,7 +1897,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -1916,7 +1911,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -1930,7 +1925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -1944,7 +1939,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -1958,7 +1953,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -1972,7 +1967,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -1986,7 +1981,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2000,7 +1995,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2014,7 +2009,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2028,7 +2023,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2042,7 +2037,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2056,7 +2051,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2070,7 +2065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2084,7 +2079,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2098,7 +2093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2112,7 +2107,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2126,7 +2121,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2140,7 +2135,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2154,7 +2149,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2168,7 +2163,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2182,7 +2177,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2196,7 +2191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2210,7 +2205,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2224,7 +2219,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2238,7 +2233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2252,7 +2247,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2266,7 +2261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2280,7 +2275,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2294,7 +2289,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2308,7 +2303,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2322,7 +2317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2336,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2350,7 +2345,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2364,7 +2359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2378,7 +2373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2392,7 +2387,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2406,7 +2401,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2420,7 +2415,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2434,7 +2429,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2462,7 +2457,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2476,7 +2471,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2490,7 +2485,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -2504,7 +2499,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -2518,7 +2513,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -2532,7 +2527,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -2546,7 +2541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -2560,7 +2555,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -2574,7 +2569,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -2588,7 +2583,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -2602,7 +2597,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -2616,7 +2611,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -2630,7 +2625,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -2644,7 +2639,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2658,7 +2653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -2672,7 +2667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -2686,7 +2681,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -2700,7 +2695,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -2714,7 +2709,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -2728,7 +2723,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -2742,7 +2737,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -2756,7 +2751,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -2770,7 +2765,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -2784,7 +2779,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -2798,7 +2793,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -2812,7 +2807,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -2826,7 +2821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -2840,7 +2835,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2854,7 +2849,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -2868,7 +2863,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -2882,7 +2877,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -2896,7 +2891,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -2910,7 +2905,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -2924,7 +2919,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -2938,7 +2933,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -2952,7 +2947,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -2966,7 +2961,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -2980,7 +2975,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -2994,7 +2989,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3008,7 +3003,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3022,7 +3017,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3036,7 +3031,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -3050,7 +3045,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3064,7 +3059,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>142</v>
       </c>
@@ -3078,7 +3073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>142</v>
       </c>
@@ -3092,7 +3087,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>142</v>
       </c>
@@ -3106,7 +3101,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>142</v>
       </c>
@@ -3120,7 +3115,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>142</v>
       </c>
@@ -3134,7 +3129,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>142</v>
       </c>
@@ -3148,7 +3143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>142</v>
       </c>
@@ -3162,7 +3157,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>142</v>
       </c>
@@ -3176,7 +3171,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>142</v>
       </c>
@@ -3190,7 +3185,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>142</v>
       </c>
@@ -3204,7 +3199,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>142</v>
       </c>
@@ -3218,7 +3213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>142</v>
       </c>
@@ -3232,7 +3227,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>142</v>
       </c>
@@ -3246,7 +3241,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>142</v>
       </c>
@@ -3260,7 +3255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>142</v>
       </c>
@@ -3274,7 +3269,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>142</v>
       </c>
@@ -3288,7 +3283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>142</v>
       </c>
@@ -3302,7 +3297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>142</v>
       </c>
@@ -3316,7 +3311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>142</v>
       </c>
@@ -3330,7 +3325,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>142</v>
       </c>
@@ -3344,7 +3339,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>142</v>
       </c>
@@ -3358,7 +3353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>142</v>
       </c>
@@ -3372,7 +3367,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>142</v>
       </c>
@@ -3386,7 +3381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>142</v>
       </c>
@@ -3400,7 +3395,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>142</v>
       </c>
@@ -3414,7 +3409,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>142</v>
       </c>
@@ -3428,7 +3423,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>142</v>
       </c>
@@ -3442,7 +3437,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>142</v>
       </c>
@@ -3456,7 +3451,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>142</v>
       </c>
@@ -3470,7 +3465,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>142</v>
       </c>
@@ -3484,7 +3479,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>142</v>
       </c>
@@ -3498,7 +3493,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>142</v>
       </c>
@@ -3512,7 +3507,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>142</v>
       </c>
@@ -3526,7 +3521,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>142</v>
       </c>
@@ -3540,7 +3535,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>142</v>
       </c>
@@ -3554,7 +3549,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>142</v>
       </c>
@@ -3568,7 +3563,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>142</v>
       </c>
@@ -3582,7 +3577,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>142</v>
       </c>
@@ -3596,7 +3591,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>142</v>
       </c>
@@ -3610,7 +3605,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>142</v>
       </c>
@@ -3624,7 +3619,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>142</v>
       </c>
@@ -3638,7 +3633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>142</v>
       </c>
@@ -3652,7 +3647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>142</v>
       </c>
@@ -3666,7 +3661,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>142</v>
       </c>
@@ -3680,7 +3675,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>142</v>
       </c>
@@ -3694,7 +3689,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>142</v>
       </c>
@@ -3708,7 +3703,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>142</v>
       </c>
@@ -3722,7 +3717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>142</v>
       </c>
@@ -3736,7 +3731,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>142</v>
       </c>
@@ -3750,7 +3745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>142</v>
       </c>
@@ -3764,7 +3759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>142</v>
       </c>
@@ -3778,7 +3773,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>142</v>
       </c>
@@ -3792,7 +3787,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>142</v>
       </c>
@@ -3806,7 +3801,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>142</v>
       </c>
@@ -3820,7 +3815,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>142</v>
       </c>
@@ -3834,7 +3829,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>142</v>
       </c>
@@ -3848,7 +3843,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>142</v>
       </c>
@@ -3862,7 +3857,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>142</v>
       </c>
@@ -3876,7 +3871,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>142</v>
       </c>
@@ -3890,7 +3885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>142</v>
       </c>
@@ -3904,7 +3899,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>142</v>
       </c>
@@ -3918,7 +3913,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>142</v>
       </c>
@@ -3932,7 +3927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>142</v>
       </c>
@@ -3946,7 +3941,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>142</v>
       </c>
@@ -3960,7 +3955,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>142</v>
       </c>
@@ -3974,7 +3969,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>142</v>
       </c>
@@ -3988,7 +3983,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>142</v>
       </c>
@@ -4002,7 +3997,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>142</v>
       </c>
@@ -4016,7 +4011,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>142</v>
       </c>
@@ -4030,7 +4025,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>142</v>
       </c>
@@ -4044,7 +4039,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>142</v>
       </c>
@@ -4058,7 +4053,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>142</v>
       </c>
@@ -4072,7 +4067,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>142</v>
       </c>
@@ -4086,7 +4081,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>142</v>
       </c>
@@ -4100,7 +4095,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>142</v>
       </c>
@@ -4114,7 +4109,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>142</v>
       </c>
@@ -4128,7 +4123,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>142</v>
       </c>
@@ -4142,7 +4137,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>142</v>
       </c>
@@ -4156,7 +4151,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>142</v>
       </c>
@@ -4170,7 +4165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>142</v>
       </c>
@@ -4184,7 +4179,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>142</v>
       </c>
@@ -4198,7 +4193,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>142</v>
       </c>
@@ -4212,7 +4207,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>142</v>
       </c>
@@ -4226,7 +4221,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>142</v>
       </c>
@@ -4240,7 +4235,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>142</v>
       </c>
@@ -4254,7 +4249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>142</v>
       </c>
@@ -4268,7 +4263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>142</v>
       </c>
@@ -4282,7 +4277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>142</v>
       </c>
@@ -4296,7 +4291,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>142</v>
       </c>
@@ -4310,7 +4305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>142</v>
       </c>
@@ -4324,7 +4319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>142</v>
       </c>
@@ -4338,7 +4333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>142</v>
       </c>
@@ -4352,7 +4347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>142</v>
       </c>
@@ -4366,7 +4361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>142</v>
       </c>
@@ -4380,7 +4375,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>142</v>
       </c>
@@ -4394,7 +4389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>142</v>
       </c>
@@ -4408,7 +4403,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>142</v>
       </c>
@@ -4422,7 +4417,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>142</v>
       </c>
@@ -4436,7 +4431,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>142</v>
       </c>
@@ -4450,7 +4445,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>142</v>
       </c>
@@ -4464,7 +4459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>142</v>
       </c>
@@ -4478,7 +4473,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>142</v>
       </c>
@@ -4492,7 +4487,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>142</v>
       </c>
@@ -4506,7 +4501,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>142</v>
       </c>
@@ -4520,7 +4515,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>142</v>
       </c>
@@ -4534,7 +4529,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>142</v>
       </c>
@@ -4548,7 +4543,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>142</v>
       </c>
@@ -4562,7 +4557,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>142</v>
       </c>
@@ -4576,7 +4571,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>142</v>
       </c>
@@ -4590,7 +4585,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>142</v>
       </c>
@@ -4604,7 +4599,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>142</v>
       </c>
@@ -4618,7 +4613,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>142</v>
       </c>
@@ -4632,7 +4627,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>142</v>
       </c>
@@ -4646,7 +4641,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>142</v>
       </c>
@@ -4660,7 +4655,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>142</v>
       </c>
@@ -4674,7 +4669,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>142</v>
       </c>
@@ -4688,7 +4683,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>142</v>
       </c>
@@ -4702,7 +4697,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>142</v>
       </c>
@@ -4716,7 +4711,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>142</v>
       </c>
@@ -4730,7 +4725,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>142</v>
       </c>
@@ -4744,7 +4739,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>142</v>
       </c>
@@ -4758,7 +4753,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>142</v>
       </c>
@@ -4772,7 +4767,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>142</v>
       </c>
@@ -4786,7 +4781,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>142</v>
       </c>
@@ -4800,7 +4795,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>142</v>
       </c>
@@ -4814,7 +4809,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>142</v>
       </c>
@@ -4828,7 +4823,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>142</v>
       </c>
@@ -4842,7 +4837,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>142</v>
       </c>
@@ -4856,7 +4851,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>142</v>
       </c>
@@ -4870,7 +4865,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>142</v>
       </c>
@@ -4884,7 +4879,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>142</v>
       </c>
@@ -4898,7 +4893,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>142</v>
       </c>
@@ -4912,7 +4907,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>142</v>
       </c>
@@ -4926,7 +4921,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>142</v>
       </c>
@@ -4940,7 +4935,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>142</v>
       </c>
@@ -4954,7 +4949,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>142</v>
       </c>
@@ -4968,7 +4963,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>142</v>
       </c>
@@ -4982,7 +4977,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>142</v>
       </c>
@@ -4996,7 +4991,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>142</v>
       </c>
@@ -5010,7 +5005,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>142</v>
       </c>
@@ -5024,7 +5019,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>142</v>
       </c>
@@ -5038,7 +5033,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>142</v>
       </c>
@@ -5052,7 +5047,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>142</v>
       </c>
@@ -5066,7 +5061,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>142</v>
       </c>
@@ -5080,7 +5075,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>142</v>
       </c>
@@ -5094,7 +5089,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>142</v>
       </c>
@@ -5108,7 +5103,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>142</v>
       </c>
@@ -5122,7 +5117,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>142</v>
       </c>
@@ -5136,7 +5131,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>142</v>
       </c>
@@ -5150,7 +5145,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>142</v>
       </c>
@@ -5164,7 +5159,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>142</v>
       </c>
@@ -5178,7 +5173,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>142</v>
       </c>
@@ -5192,7 +5187,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>142</v>
       </c>
@@ -5206,7 +5201,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>142</v>
       </c>
@@ -5220,7 +5215,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>142</v>
       </c>
@@ -5234,7 +5229,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>168</v>
       </c>
@@ -5248,7 +5243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>168</v>
       </c>
@@ -5262,7 +5257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>168</v>
       </c>
@@ -5276,7 +5271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>168</v>
       </c>
@@ -5290,7 +5285,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>168</v>
       </c>
@@ -5304,7 +5299,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>168</v>
       </c>
@@ -5318,7 +5313,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>168</v>
       </c>
@@ -5332,7 +5327,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>168</v>
       </c>
@@ -5346,7 +5341,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>168</v>
       </c>
@@ -5360,7 +5355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>168</v>
       </c>
@@ -5374,7 +5369,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>168</v>
       </c>
@@ -5388,7 +5383,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>168</v>
       </c>
@@ -5402,7 +5397,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>168</v>
       </c>
@@ -5416,7 +5411,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>168</v>
       </c>
@@ -5430,7 +5425,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>168</v>
       </c>
@@ -5444,7 +5439,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>168</v>
       </c>
@@ -5458,7 +5453,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>168</v>
       </c>
@@ -5472,7 +5467,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>168</v>
       </c>
@@ -5486,7 +5481,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>168</v>
       </c>
@@ -5500,7 +5495,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>168</v>
       </c>
@@ -5514,7 +5509,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>168</v>
       </c>
@@ -5528,7 +5523,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>168</v>
       </c>
@@ -5542,7 +5537,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>168</v>
       </c>
@@ -5556,7 +5551,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>168</v>
       </c>
@@ -5570,7 +5565,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>168</v>
       </c>
@@ -5584,7 +5579,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>168</v>
       </c>
@@ -5598,7 +5593,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>168</v>
       </c>
@@ -5612,7 +5607,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>168</v>
       </c>
@@ -5626,7 +5621,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>168</v>
       </c>
@@ -5640,7 +5635,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>168</v>
       </c>
@@ -5654,7 +5649,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>168</v>
       </c>
@@ -5668,7 +5663,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>168</v>
       </c>
@@ -5682,7 +5677,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>168</v>
       </c>
@@ -5696,7 +5691,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>168</v>
       </c>
@@ -5710,7 +5705,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>168</v>
       </c>
@@ -5724,7 +5719,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>168</v>
       </c>
@@ -5738,7 +5733,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>168</v>
       </c>
@@ -5752,7 +5747,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>168</v>
       </c>
@@ -5766,7 +5761,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>168</v>
       </c>
@@ -5780,7 +5775,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>168</v>
       </c>
@@ -5794,7 +5789,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>168</v>
       </c>
@@ -5808,7 +5803,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>168</v>
       </c>
@@ -5822,7 +5817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>168</v>
       </c>
@@ -5836,7 +5831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>168</v>
       </c>
@@ -5850,7 +5845,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>168</v>
       </c>
@@ -5864,7 +5859,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>168</v>
       </c>
@@ -5878,7 +5873,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>168</v>
       </c>
@@ -5892,7 +5887,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>168</v>
       </c>
@@ -5906,7 +5901,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>168</v>
       </c>
@@ -5920,7 +5915,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>168</v>
       </c>
@@ -5934,7 +5929,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>168</v>
       </c>
@@ -5948,7 +5943,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>168</v>
       </c>
@@ -5962,7 +5957,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>168</v>
       </c>
@@ -5976,7 +5971,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>168</v>
       </c>
@@ -5990,7 +5985,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>168</v>
       </c>
@@ -6004,7 +5999,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>168</v>
       </c>
@@ -6018,7 +6013,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>168</v>
       </c>
@@ -6032,7 +6027,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>168</v>
       </c>
@@ -6046,7 +6041,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>168</v>
       </c>
@@ -6060,7 +6055,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>168</v>
       </c>
@@ -6074,7 +6069,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>168</v>
       </c>
@@ -6088,7 +6083,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>168</v>
       </c>
@@ -6102,7 +6097,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>168</v>
       </c>
@@ -6116,7 +6111,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>168</v>
       </c>
@@ -6130,7 +6125,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>168</v>
       </c>
@@ -6144,7 +6139,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>168</v>
       </c>
@@ -6158,7 +6153,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>168</v>
       </c>
@@ -6172,7 +6167,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>168</v>
       </c>
@@ -6186,7 +6181,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>168</v>
       </c>
@@ -6200,7 +6195,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>168</v>
       </c>
@@ -6214,7 +6209,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>168</v>
       </c>
@@ -6228,7 +6223,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>168</v>
       </c>
@@ -6242,7 +6237,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>168</v>
       </c>
@@ -6256,7 +6251,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>168</v>
       </c>
@@ -6270,7 +6265,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>168</v>
       </c>
@@ -6284,7 +6279,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>168</v>
       </c>
@@ -6298,7 +6293,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>168</v>
       </c>
@@ -6312,7 +6307,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>168</v>
       </c>
@@ -6326,7 +6321,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>168</v>
       </c>
@@ -6340,7 +6335,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>168</v>
       </c>
@@ -6354,7 +6349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>168</v>
       </c>
@@ -6368,7 +6363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>168</v>
       </c>
@@ -6382,7 +6377,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>168</v>
       </c>
@@ -6396,7 +6391,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>168</v>
       </c>
@@ -6410,7 +6405,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>168</v>
       </c>
@@ -6424,7 +6419,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>168</v>
       </c>
@@ -6438,7 +6433,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>168</v>
       </c>
@@ -6452,7 +6447,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>168</v>
       </c>
@@ -6466,7 +6461,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>168</v>
       </c>
@@ -6480,7 +6475,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>168</v>
       </c>
@@ -6494,7 +6489,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>168</v>
       </c>
@@ -6508,7 +6503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>168</v>
       </c>
@@ -6522,7 +6517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>168</v>
       </c>
@@ -6536,7 +6531,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>168</v>
       </c>
@@ -6550,7 +6545,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>168</v>
       </c>
@@ -6564,7 +6559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>168</v>
       </c>
@@ -6578,7 +6573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>168</v>
       </c>
@@ -6592,7 +6587,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>168</v>
       </c>
@@ -6606,7 +6601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>168</v>
       </c>
@@ -6620,7 +6615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>168</v>
       </c>
@@ -6634,7 +6629,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>168</v>
       </c>
@@ -6648,7 +6643,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>168</v>
       </c>
@@ -6662,7 +6657,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>168</v>
       </c>
@@ -6676,7 +6671,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>168</v>
       </c>
@@ -6690,7 +6685,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>168</v>
       </c>
@@ -6704,7 +6699,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>168</v>
       </c>
@@ -6718,7 +6713,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>168</v>
       </c>
@@ -6732,7 +6727,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>168</v>
       </c>
@@ -6746,7 +6741,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>168</v>
       </c>
@@ -6760,7 +6755,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>168</v>
       </c>
@@ -6774,7 +6769,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>168</v>
       </c>
@@ -6788,7 +6783,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>168</v>
       </c>
@@ -6802,7 +6797,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>168</v>
       </c>
@@ -6816,7 +6811,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>168</v>
       </c>
@@ -6830,7 +6825,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>168</v>
       </c>
@@ -6844,7 +6839,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>168</v>
       </c>
@@ -6858,7 +6853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>168</v>
       </c>
@@ -6872,7 +6867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>168</v>
       </c>
@@ -6886,7 +6881,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>168</v>
       </c>
@@ -6900,7 +6895,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>168</v>
       </c>
@@ -6914,7 +6909,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>168</v>
       </c>
@@ -6928,7 +6923,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>168</v>
       </c>
@@ -6942,7 +6937,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>168</v>
       </c>
@@ -6956,7 +6951,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>168</v>
       </c>
@@ -6970,7 +6965,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>168</v>
       </c>
@@ -6984,7 +6979,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>168</v>
       </c>
@@ -6998,7 +6993,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>168</v>
       </c>
@@ -7012,7 +7007,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>168</v>
       </c>
@@ -7026,7 +7021,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>168</v>
       </c>
@@ -7040,7 +7035,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>168</v>
       </c>
@@ -7054,7 +7049,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>168</v>
       </c>
@@ -7068,7 +7063,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>168</v>
       </c>
@@ -7082,7 +7077,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>168</v>
       </c>
@@ -7096,7 +7091,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>168</v>
       </c>
@@ -7110,7 +7105,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>168</v>
       </c>
@@ -7124,7 +7119,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>168</v>
       </c>
@@ -7138,7 +7133,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>168</v>
       </c>
@@ -7152,7 +7147,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>168</v>
       </c>
@@ -7166,7 +7161,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>168</v>
       </c>
@@ -7180,7 +7175,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>168</v>
       </c>
@@ -7194,7 +7189,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>168</v>
       </c>
@@ -7208,7 +7203,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>168</v>
       </c>
@@ -7222,7 +7217,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>168</v>
       </c>
@@ -7236,7 +7231,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>168</v>
       </c>
@@ -7250,7 +7245,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>168</v>
       </c>
@@ -7264,7 +7259,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>168</v>
       </c>
@@ -7278,7 +7273,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>168</v>
       </c>
@@ -7292,7 +7287,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>168</v>
       </c>
@@ -7306,7 +7301,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>168</v>
       </c>
@@ -7320,7 +7315,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>168</v>
       </c>
@@ -7334,7 +7329,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>168</v>
       </c>
@@ -7348,7 +7343,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>181</v>
       </c>
@@ -7362,7 +7357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>181</v>
       </c>
@@ -7376,7 +7371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>181</v>
       </c>
@@ -7390,7 +7385,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>181</v>
       </c>
@@ -7404,7 +7399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>181</v>
       </c>
@@ -7418,7 +7413,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>181</v>
       </c>
@@ -7432,7 +7427,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>181</v>
       </c>
@@ -7446,7 +7441,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>181</v>
       </c>
@@ -7460,7 +7455,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>181</v>
       </c>
@@ -7474,7 +7469,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>181</v>
       </c>
@@ -7488,7 +7483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>181</v>
       </c>
@@ -7502,7 +7497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>181</v>
       </c>
@@ -7516,7 +7511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>181</v>
       </c>
@@ -7530,7 +7525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>181</v>
       </c>
@@ -7544,7 +7539,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>181</v>
       </c>
@@ -7558,7 +7553,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>181</v>
       </c>
@@ -7572,7 +7567,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>181</v>
       </c>
@@ -7586,7 +7581,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>181</v>
       </c>
@@ -7600,7 +7595,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>181</v>
       </c>
@@ -7614,7 +7609,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>181</v>
       </c>
@@ -7628,7 +7623,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>181</v>
       </c>
@@ -7642,7 +7637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>181</v>
       </c>
@@ -7656,7 +7651,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>181</v>
       </c>
@@ -7670,7 +7665,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>181</v>
       </c>
@@ -7684,7 +7679,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>181</v>
       </c>
@@ -7698,7 +7693,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>181</v>
       </c>
@@ -7712,7 +7707,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>181</v>
       </c>
@@ -7726,7 +7721,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>181</v>
       </c>
@@ -7740,7 +7735,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>181</v>
       </c>
@@ -7754,7 +7749,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>181</v>
       </c>
@@ -7768,7 +7763,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>181</v>
       </c>
@@ -7782,7 +7777,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>181</v>
       </c>
@@ -7796,7 +7791,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>181</v>
       </c>
@@ -7810,7 +7805,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>181</v>
       </c>
@@ -7824,7 +7819,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>181</v>
       </c>
@@ -7838,7 +7833,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>181</v>
       </c>
@@ -7852,7 +7847,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>181</v>
       </c>
@@ -7866,7 +7861,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>181</v>
       </c>
@@ -7880,7 +7875,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>181</v>
       </c>
@@ -7894,7 +7889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>181</v>
       </c>
@@ -7908,7 +7903,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>181</v>
       </c>
@@ -7922,7 +7917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>181</v>
       </c>
@@ -7936,7 +7931,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>181</v>
       </c>
@@ -7950,7 +7945,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>181</v>
       </c>
@@ -7964,7 +7959,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>181</v>
       </c>
@@ -7978,7 +7973,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>181</v>
       </c>
@@ -7992,7 +7987,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>181</v>
       </c>
@@ -8006,7 +8001,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>181</v>
       </c>
@@ -8020,7 +8015,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>181</v>
       </c>
@@ -8034,7 +8029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>181</v>
       </c>
@@ -8048,7 +8043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>181</v>
       </c>
@@ -8062,7 +8057,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>181</v>
       </c>
@@ -8076,7 +8071,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>181</v>
       </c>
@@ -8090,7 +8085,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>181</v>
       </c>
@@ -8104,7 +8099,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>181</v>
       </c>
@@ -8118,7 +8113,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>181</v>
       </c>
@@ -8132,7 +8127,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>181</v>
       </c>
@@ -8146,7 +8141,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>181</v>
       </c>
@@ -8160,7 +8155,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>181</v>
       </c>
@@ -8174,7 +8169,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>181</v>
       </c>
@@ -8188,7 +8183,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>181</v>
       </c>
@@ -8202,7 +8197,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>181</v>
       </c>
@@ -8216,7 +8211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>181</v>
       </c>
@@ -8230,7 +8225,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>181</v>
       </c>
@@ -8244,7 +8239,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>181</v>
       </c>
@@ -8258,7 +8253,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>181</v>
       </c>
@@ -8272,7 +8267,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>181</v>
       </c>
@@ -8286,7 +8281,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>181</v>
       </c>
@@ -8300,7 +8295,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>181</v>
       </c>
@@ -8314,7 +8309,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>181</v>
       </c>
@@ -8328,7 +8323,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>181</v>
       </c>
@@ -8342,7 +8337,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>181</v>
       </c>
@@ -8356,7 +8351,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>181</v>
       </c>
@@ -8370,7 +8365,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>181</v>
       </c>
@@ -8384,7 +8379,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>181</v>
       </c>
@@ -8398,7 +8393,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>181</v>
       </c>
@@ -8412,7 +8407,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>181</v>
       </c>
@@ -8426,7 +8421,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>181</v>
       </c>
@@ -8440,7 +8435,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>181</v>
       </c>
@@ -8454,7 +8449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>181</v>
       </c>
@@ -8468,7 +8463,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>181</v>
       </c>
@@ -8482,7 +8477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>181</v>
       </c>
@@ -8496,7 +8491,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>181</v>
       </c>
@@ -8510,7 +8505,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>181</v>
       </c>
@@ -8524,7 +8519,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>181</v>
       </c>
@@ -8538,7 +8533,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>181</v>
       </c>
@@ -8552,7 +8547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>181</v>
       </c>
@@ -8566,7 +8561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>181</v>
       </c>
@@ -8580,7 +8575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>181</v>
       </c>
@@ -8594,7 +8589,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>181</v>
       </c>
@@ -8608,7 +8603,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>181</v>
       </c>
@@ -8622,7 +8617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>181</v>
       </c>
@@ -8636,7 +8631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>181</v>
       </c>
@@ -8650,7 +8645,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>181</v>
       </c>
@@ -8664,7 +8659,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>181</v>
       </c>
@@ -8678,7 +8673,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>181</v>
       </c>
@@ -8692,7 +8687,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>181</v>
       </c>
@@ -8706,7 +8701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>181</v>
       </c>
@@ -8720,7 +8715,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>181</v>
       </c>
@@ -8734,7 +8729,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>181</v>
       </c>
@@ -8748,7 +8743,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>181</v>
       </c>
@@ -8762,7 +8757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>181</v>
       </c>
@@ -8776,7 +8771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>181</v>
       </c>
@@ -8790,7 +8785,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>181</v>
       </c>
@@ -8804,7 +8799,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>181</v>
       </c>
@@ -8818,7 +8813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>181</v>
       </c>
@@ -8832,7 +8827,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>181</v>
       </c>
@@ -8846,7 +8841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>181</v>
       </c>
@@ -8860,7 +8855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>181</v>
       </c>
@@ -8874,7 +8869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>181</v>
       </c>
@@ -8888,7 +8883,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>181</v>
       </c>
@@ -8902,7 +8897,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>181</v>
       </c>
@@ -8916,7 +8911,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>181</v>
       </c>
@@ -8930,7 +8925,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>181</v>
       </c>
@@ -8944,7 +8939,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>181</v>
       </c>
@@ -8958,7 +8953,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>181</v>
       </c>
@@ -8972,7 +8967,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>181</v>
       </c>
@@ -8986,7 +8981,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>181</v>
       </c>
@@ -9000,7 +8995,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>181</v>
       </c>
@@ -9014,7 +9009,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>181</v>
       </c>
@@ -9028,7 +9023,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>181</v>
       </c>
@@ -9042,7 +9037,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>181</v>
       </c>
@@ -9056,7 +9051,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>181</v>
       </c>
@@ -9070,7 +9065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>181</v>
       </c>
@@ -9084,7 +9079,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>181</v>
       </c>
@@ -9098,7 +9093,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>181</v>
       </c>
@@ -9112,7 +9107,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>181</v>
       </c>
@@ -9126,7 +9121,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>181</v>
       </c>
@@ -9140,7 +9135,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>181</v>
       </c>
@@ -9154,7 +9149,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>181</v>
       </c>
@@ -9168,7 +9163,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>181</v>
       </c>
@@ -9182,7 +9177,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>181</v>
       </c>
@@ -9196,7 +9191,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>181</v>
       </c>
@@ -9210,7 +9205,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>181</v>
       </c>
@@ -9224,7 +9219,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>181</v>
       </c>
@@ -9238,7 +9233,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>181</v>
       </c>
@@ -9252,7 +9247,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>181</v>
       </c>
@@ -9266,7 +9261,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>181</v>
       </c>
@@ -9280,7 +9275,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>181</v>
       </c>
@@ -9294,7 +9289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>181</v>
       </c>
@@ -9308,7 +9303,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>181</v>
       </c>
@@ -9322,7 +9317,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>181</v>
       </c>
@@ -9336,7 +9331,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>181</v>
       </c>
@@ -9350,7 +9345,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>181</v>
       </c>
@@ -9364,7 +9359,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>181</v>
       </c>
@@ -9378,7 +9373,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>181</v>
       </c>
@@ -9392,7 +9387,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>181</v>
       </c>
@@ -9406,7 +9401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>181</v>
       </c>
@@ -9420,7 +9415,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>181</v>
       </c>
@@ -9434,7 +9429,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>181</v>
       </c>
@@ -9448,7 +9443,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>181</v>
       </c>
@@ -9462,7 +9457,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>181</v>
       </c>
@@ -9476,7 +9471,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>181</v>
       </c>
@@ -9490,7 +9485,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>181</v>
       </c>
@@ -9504,7 +9499,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>181</v>
       </c>
@@ -9518,7 +9513,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>181</v>
       </c>
@@ -9532,7 +9527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>190</v>
       </c>
@@ -9546,7 +9541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>190</v>
       </c>
@@ -9560,7 +9555,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>190</v>
       </c>
@@ -9574,7 +9569,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>190</v>
       </c>
@@ -9588,7 +9583,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>190</v>
       </c>
@@ -9602,7 +9597,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>190</v>
       </c>
@@ -9616,7 +9611,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>190</v>
       </c>
@@ -9630,7 +9625,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>190</v>
       </c>
@@ -9644,7 +9639,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>190</v>
       </c>
@@ -9658,7 +9653,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>190</v>
       </c>
@@ -9672,7 +9667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>190</v>
       </c>
@@ -9686,7 +9681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>190</v>
       </c>
@@ -9700,7 +9695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>190</v>
       </c>
@@ -9714,7 +9709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>190</v>
       </c>
@@ -9728,7 +9723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>190</v>
       </c>
@@ -9742,7 +9737,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>190</v>
       </c>
@@ -9756,7 +9751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>190</v>
       </c>
@@ -9770,7 +9765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>190</v>
       </c>
@@ -9784,7 +9779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>190</v>
       </c>
@@ -9798,7 +9793,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>190</v>
       </c>
@@ -9812,7 +9807,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>190</v>
       </c>
@@ -9826,7 +9821,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>190</v>
       </c>
@@ -9840,7 +9835,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>190</v>
       </c>
@@ -9854,7 +9849,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>190</v>
       </c>
@@ -9868,7 +9863,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>190</v>
       </c>
@@ -9882,7 +9877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>190</v>
       </c>
@@ -9896,7 +9891,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>190</v>
       </c>
@@ -9910,7 +9905,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>190</v>
       </c>
@@ -9924,7 +9919,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>190</v>
       </c>
@@ -9938,7 +9933,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>190</v>
       </c>
@@ -9952,7 +9947,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>190</v>
       </c>
@@ -9966,7 +9961,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>190</v>
       </c>
@@ -9980,7 +9975,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>190</v>
       </c>
@@ -9994,7 +9989,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>190</v>
       </c>
@@ -10008,7 +10003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>190</v>
       </c>
@@ -10022,7 +10017,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>190</v>
       </c>
@@ -10036,7 +10031,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>190</v>
       </c>
@@ -10050,7 +10045,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>190</v>
       </c>
@@ -10064,7 +10059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>190</v>
       </c>
@@ -10078,7 +10073,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>190</v>
       </c>
@@ -10092,7 +10087,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>190</v>
       </c>
@@ -10106,7 +10101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>190</v>
       </c>
@@ -10120,7 +10115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>190</v>
       </c>
@@ -10134,7 +10129,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>190</v>
       </c>
@@ -10148,7 +10143,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>190</v>
       </c>
@@ -10162,7 +10157,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>190</v>
       </c>
@@ -10176,7 +10171,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>190</v>
       </c>
@@ -10190,7 +10185,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>190</v>
       </c>
@@ -10204,7 +10199,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>190</v>
       </c>
@@ -10218,7 +10213,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>190</v>
       </c>
@@ -10232,7 +10227,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>190</v>
       </c>
@@ -10246,7 +10241,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>190</v>
       </c>
@@ -10260,7 +10255,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>190</v>
       </c>
@@ -10274,7 +10269,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>190</v>
       </c>
@@ -10288,7 +10283,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>190</v>
       </c>
@@ -10302,7 +10297,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>190</v>
       </c>
@@ -10316,7 +10311,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>190</v>
       </c>
@@ -10330,7 +10325,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>190</v>
       </c>
@@ -10344,7 +10339,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>190</v>
       </c>
@@ -10358,7 +10353,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>190</v>
       </c>
@@ -10372,7 +10367,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>190</v>
       </c>
@@ -10386,7 +10381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>190</v>
       </c>
@@ -10400,7 +10395,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>190</v>
       </c>
@@ -10414,7 +10409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>190</v>
       </c>
@@ -10428,7 +10423,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>190</v>
       </c>
@@ -10442,7 +10437,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>190</v>
       </c>
@@ -10456,7 +10451,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>190</v>
       </c>
@@ -10470,7 +10465,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>190</v>
       </c>
@@ -10484,7 +10479,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>190</v>
       </c>
@@ -10498,7 +10493,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>190</v>
       </c>
@@ -10512,7 +10507,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>190</v>
       </c>
@@ -10526,7 +10521,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>190</v>
       </c>
@@ -10540,7 +10535,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>190</v>
       </c>
@@ -10554,7 +10549,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>190</v>
       </c>
@@ -10568,7 +10563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>190</v>
       </c>
@@ -10582,7 +10577,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>190</v>
       </c>
@@ -10596,7 +10591,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>190</v>
       </c>
@@ -10610,7 +10605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>190</v>
       </c>
@@ -10624,7 +10619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>190</v>
       </c>
@@ -10638,7 +10633,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>190</v>
       </c>
@@ -10652,7 +10647,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>190</v>
       </c>
@@ -10666,7 +10661,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>190</v>
       </c>
@@ -10680,7 +10675,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>190</v>
       </c>
@@ -10694,7 +10689,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>190</v>
       </c>
@@ -10708,7 +10703,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>190</v>
       </c>
@@ -10722,7 +10717,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>190</v>
       </c>
@@ -10736,7 +10731,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>190</v>
       </c>
@@ -10750,7 +10745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>190</v>
       </c>
@@ -10764,7 +10759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>190</v>
       </c>
@@ -10778,7 +10773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>190</v>
       </c>
@@ -10792,7 +10787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>190</v>
       </c>
@@ -10806,7 +10801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>190</v>
       </c>
@@ -10820,7 +10815,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>190</v>
       </c>
@@ -10834,7 +10829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>190</v>
       </c>
@@ -10848,7 +10843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>190</v>
       </c>
@@ -10862,7 +10857,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>190</v>
       </c>
@@ -10876,7 +10871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>190</v>
       </c>
@@ -10890,7 +10885,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>190</v>
       </c>
@@ -10904,7 +10899,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>190</v>
       </c>
@@ -10918,7 +10913,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>190</v>
       </c>
@@ -10932,7 +10927,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>190</v>
       </c>
@@ -10946,7 +10941,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>190</v>
       </c>
@@ -10960,7 +10955,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>190</v>
       </c>
@@ -10974,7 +10969,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>190</v>
       </c>
@@ -10988,7 +10983,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>190</v>
       </c>
@@ -11002,7 +10997,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>190</v>
       </c>
@@ -11016,7 +11011,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>190</v>
       </c>
@@ -11030,7 +11025,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>190</v>
       </c>
@@ -11044,7 +11039,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>190</v>
       </c>
@@ -11058,7 +11053,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>190</v>
       </c>
@@ -11072,7 +11067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>190</v>
       </c>
@@ -11086,7 +11081,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>190</v>
       </c>
@@ -11100,7 +11095,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>190</v>
       </c>
@@ -11114,7 +11109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>190</v>
       </c>
@@ -11128,7 +11123,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>190</v>
       </c>
@@ -11142,7 +11137,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>190</v>
       </c>
@@ -11156,7 +11151,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>190</v>
       </c>
@@ -11170,7 +11165,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>190</v>
       </c>
@@ -11184,7 +11179,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>190</v>
       </c>
@@ -11198,7 +11193,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>190</v>
       </c>
@@ -11212,7 +11207,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>190</v>
       </c>
@@ -11226,7 +11221,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>190</v>
       </c>
@@ -11240,7 +11235,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>190</v>
       </c>
@@ -11254,7 +11249,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>190</v>
       </c>
@@ -11268,7 +11263,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>190</v>
       </c>
@@ -11282,7 +11277,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>190</v>
       </c>
@@ -11296,7 +11291,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>190</v>
       </c>
@@ -11310,7 +11305,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>190</v>
       </c>
@@ -11324,7 +11319,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>190</v>
       </c>
@@ -11338,7 +11333,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>190</v>
       </c>
@@ -11352,7 +11347,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>190</v>
       </c>
@@ -11366,7 +11361,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>190</v>
       </c>
@@ -11380,7 +11375,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>190</v>
       </c>
@@ -11394,7 +11389,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>190</v>
       </c>
@@ -11408,7 +11403,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>190</v>
       </c>
@@ -11422,7 +11417,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>190</v>
       </c>
@@ -11436,7 +11431,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>190</v>
       </c>
@@ -11450,7 +11445,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>190</v>
       </c>
@@ -11464,7 +11459,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>190</v>
       </c>
@@ -11478,7 +11473,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>190</v>
       </c>
@@ -11492,7 +11487,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>190</v>
       </c>
@@ -11506,7 +11501,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="781" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>190</v>
       </c>
@@ -11520,7 +11515,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="782" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>190</v>
       </c>
@@ -11534,7 +11529,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="783" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>190</v>
       </c>
@@ -11548,7 +11543,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="784" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>190</v>
       </c>
@@ -11562,7 +11557,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>190</v>
       </c>
@@ -11576,7 +11571,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>190</v>
       </c>
@@ -11590,7 +11585,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>190</v>
       </c>
@@ -11604,7 +11599,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>190</v>
       </c>
@@ -11618,7 +11613,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>190</v>
       </c>
@@ -11632,7 +11627,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>190</v>
       </c>
@@ -11648,20 +11643,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B90"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>195</v>
       </c>
@@ -11669,7 +11664,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -11677,7 +11672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -11685,7 +11680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -11693,7 +11688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -11701,7 +11696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -11709,7 +11704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -11717,7 +11712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -11725,7 +11720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -11733,7 +11728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11741,7 +11736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -11749,7 +11744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -11757,7 +11752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -11765,7 +11760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -11773,7 +11768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -11781,7 +11776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -11789,7 +11784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -11797,7 +11792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -11805,7 +11800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -11813,7 +11808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -11821,7 +11816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>143</v>
       </c>
@@ -11829,7 +11824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>144</v>
       </c>
@@ -11837,7 +11832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -11845,7 +11840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -11853,7 +11848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -11861,7 +11856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -11869,7 +11864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -11877,7 +11872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -11885,7 +11880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>126</v>
       </c>
@@ -11893,7 +11888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -11901,7 +11896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -11909,7 +11904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -11917,7 +11912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -11925,7 +11920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -11933,7 +11928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>128</v>
       </c>
@@ -11941,7 +11936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -11949,7 +11944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -11957,7 +11952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>59</v>
       </c>
@@ -11965,7 +11960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -11973,7 +11968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -11981,7 +11976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -11989,7 +11984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -11997,7 +11992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -12005,7 +12000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>83</v>
       </c>
@@ -12013,7 +12008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -12021,7 +12016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>69</v>
       </c>
@@ -12029,7 +12024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -12037,7 +12032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -12045,7 +12040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -12053,7 +12048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>72</v>
       </c>
@@ -12061,7 +12056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -12069,7 +12064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -12077,7 +12072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>149</v>
       </c>
@@ -12085,7 +12080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>129</v>
       </c>
@@ -12093,7 +12088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -12101,7 +12096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>74</v>
       </c>
@@ -12109,7 +12104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>78</v>
       </c>
@@ -12117,7 +12112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>76</v>
       </c>
@@ -12125,7 +12120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -12133,7 +12128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>137</v>
       </c>
@@ -12141,7 +12136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>136</v>
       </c>
@@ -12149,7 +12144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -12157,7 +12152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -12165,7 +12160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -12173,7 +12168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>153</v>
       </c>
@@ -12181,7 +12176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>155</v>
       </c>
@@ -12189,7 +12184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>87</v>
       </c>
@@ -12197,7 +12192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -12205,7 +12200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>99</v>
       </c>
@@ -12213,7 +12208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -12221,7 +12216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -12229,7 +12224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>164</v>
       </c>
@@ -12237,7 +12232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>134</v>
       </c>
@@ -12245,7 +12240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>103</v>
       </c>
@@ -12253,7 +12248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>104</v>
       </c>
@@ -12261,7 +12256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -12269,7 +12264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>95</v>
       </c>
@@ -12277,7 +12272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>93</v>
       </c>
@@ -12285,7 +12280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -12293,7 +12288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>138</v>
       </c>
@@ -12301,7 +12296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>139</v>
       </c>
@@ -12309,7 +12304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>106</v>
       </c>
@@ -12317,7 +12312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -12325,7 +12320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -12333,7 +12328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -12341,7 +12336,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -12349,7 +12344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>157</v>
       </c>
@@ -12357,7 +12352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>169</v>
       </c>
@@ -12365,7 +12360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>113</v>
       </c>
@@ -12373,7 +12368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -12383,6 +12378,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>